--- a/PLTR.xlsx
+++ b/PLTR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00901271-9AE6-41A0-8935-BA585537D407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DEC16C-C446-4AEA-90A9-A1CB3DD4D735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39230" yWindow="710" windowWidth="17370" windowHeight="13000" activeTab="1" xr2:uid="{AE04E6E4-A652-4DFB-A34B-BE287D9B2752}"/>
+    <workbookView xWindow="9800" yWindow="13390" windowWidth="22360" windowHeight="13220" activeTab="1" xr2:uid="{AE04E6E4-A652-4DFB-A34B-BE287D9B2752}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>177</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="L4" s="3">
         <f>L3*L2</f>
-        <v>455067</v>
+        <v>377937</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="L7" s="3">
         <f>L4-L5+L6</f>
-        <v>448629</v>
+        <v>371499</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
@@ -2193,12 +2193,10 @@
         <v>1181.0920000000001</v>
       </c>
       <c r="Z19" s="5">
-        <f>+V19*1.66</f>
-        <v>1373.68154</v>
+        <v>1410</v>
       </c>
       <c r="AA19" s="5">
-        <f>+W19*1.7</f>
-        <v>1501.1</v>
+        <v>1633</v>
       </c>
       <c r="AB19" s="5">
         <f>+X19*1.7</f>
@@ -2210,7 +2208,7 @@
       </c>
       <c r="AD19" s="5">
         <f>+Z19*1.7</f>
-        <v>2335.2586179999998</v>
+        <v>2397</v>
       </c>
       <c r="AG19" s="5">
         <v>1092.673</v>
@@ -2232,47 +2230,47 @@
       </c>
       <c r="AL19" s="5">
         <f>SUM(W19:Z19)</f>
-        <v>4441.7735400000001</v>
+        <v>4478.0920000000006</v>
       </c>
       <c r="AM19" s="5">
         <f>AL19*1.6</f>
-        <v>7106.8376640000006</v>
+        <v>7164.9472000000014</v>
       </c>
       <c r="AN19" s="5">
         <f>AM19*1.5</f>
-        <v>10660.256496000002</v>
+        <v>10747.420800000002</v>
       </c>
       <c r="AO19" s="5">
         <f>AN19*1.4</f>
-        <v>14924.359094400001</v>
+        <v>15046.389120000002</v>
       </c>
       <c r="AP19" s="5">
         <f>AO19*1.35</f>
-        <v>20147.884777440002</v>
+        <v>20312.625312000004</v>
       </c>
       <c r="AQ19" s="5">
         <f>AP19*1.3</f>
-        <v>26192.250210672002</v>
+        <v>26406.412905600006</v>
       </c>
       <c r="AR19" s="5">
         <f>AQ19*1.25</f>
-        <v>32740.312763340004</v>
+        <v>33008.016132000004</v>
       </c>
       <c r="AS19" s="5">
         <f>AR19*1.2</f>
-        <v>39288.375316008001</v>
+        <v>39609.619358400007</v>
       </c>
       <c r="AT19" s="5">
         <f>AS19*1.2</f>
-        <v>47146.050379209599</v>
+        <v>47531.543230080009</v>
       </c>
       <c r="AU19" s="5">
         <f>AT19*1.2</f>
-        <v>56575.260455051517</v>
+        <v>57037.851876096007</v>
       </c>
       <c r="AV19" s="5">
         <f>AU19*1.2</f>
-        <v>67890.312546061818</v>
+        <v>68445.422251315205</v>
       </c>
     </row>
     <row r="20" spans="2:122" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2358,7 +2356,7 @@
       </c>
       <c r="Z20" s="3">
         <f t="shared" ref="Z20" si="17">+Z19-Z21</f>
-        <v>233.52586180000003</v>
+        <v>239.70000000000005</v>
       </c>
       <c r="AG20" s="3">
         <v>352.54700000000003</v>
@@ -2380,47 +2378,47 @@
       </c>
       <c r="AL20" s="3">
         <f t="shared" si="18"/>
-        <v>888.35470799999985</v>
+        <v>895.61839999999984</v>
       </c>
       <c r="AM20" s="3">
         <f t="shared" ref="AM20" si="19">AM19-AM21</f>
-        <v>1421.3675327999999</v>
+        <v>1432.9894400000003</v>
       </c>
       <c r="AN20" s="3">
         <f t="shared" ref="AN20" si="20">AN19-AN21</f>
-        <v>2132.0512992000004</v>
+        <v>2149.48416</v>
       </c>
       <c r="AO20" s="3">
         <f t="shared" ref="AO20:AQ20" si="21">AO19-AO21</f>
-        <v>2984.8718188799994</v>
+        <v>3009.2778239999989</v>
       </c>
       <c r="AP20" s="3">
         <f t="shared" si="21"/>
-        <v>4029.5769554879989</v>
+        <v>4062.5250624</v>
       </c>
       <c r="AQ20" s="3">
         <f t="shared" si="21"/>
-        <v>5238.4500421343982</v>
+        <v>5281.2825811199982</v>
       </c>
       <c r="AR20" s="3">
         <f t="shared" ref="AR20:AV20" si="22">AR19-AR21</f>
-        <v>6548.0625526679978</v>
+        <v>6601.6032263999987</v>
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="22"/>
-        <v>7857.6750632015974</v>
+        <v>7921.9238716799991</v>
       </c>
       <c r="AT20" s="3">
         <f t="shared" si="22"/>
-        <v>9429.2100758419183</v>
+        <v>9506.3086460159975</v>
       </c>
       <c r="AU20" s="3">
         <f t="shared" si="22"/>
-        <v>11315.052091010301</v>
+        <v>11407.570375219198</v>
       </c>
       <c r="AV20" s="3">
         <f t="shared" si="22"/>
-        <v>13578.062509212359</v>
+        <v>13689.084450263035</v>
       </c>
     </row>
     <row r="21" spans="2:122" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2493,32 +2491,32 @@
         <v>528.49799999999993</v>
       </c>
       <c r="T21" s="3">
-        <f>+T19-T20</f>
+        <f t="shared" ref="T21:Y21" si="26">+T19-T20</f>
         <v>561.97400000000005</v>
       </c>
       <c r="U21" s="3">
-        <f>+U19-U20</f>
+        <f t="shared" si="26"/>
         <v>592</v>
       </c>
       <c r="V21" s="3">
-        <f>+V19-V20</f>
+        <f t="shared" si="26"/>
         <v>686.11</v>
       </c>
       <c r="W21" s="3">
-        <f>+W19-W20</f>
+        <f t="shared" si="26"/>
         <v>725.04600000000005</v>
       </c>
       <c r="X21" s="3">
-        <f>+X19-X20</f>
+        <f t="shared" si="26"/>
         <v>811.06600000000003</v>
       </c>
       <c r="Y21" s="3">
-        <f>+Y19-Y20</f>
+        <f t="shared" si="26"/>
         <v>973.78500000000008</v>
       </c>
       <c r="Z21" s="3">
-        <f t="shared" ref="Z21" si="26">+Z19*0.83</f>
-        <v>1140.1556782</v>
+        <f t="shared" ref="Z21" si="27">+Z19*0.83</f>
+        <v>1170.3</v>
       </c>
       <c r="AG21" s="3">
         <f>AG19-AG20</f>
@@ -2533,7 +2531,7 @@
         <v>1524.6967999999999</v>
       </c>
       <c r="AJ21" s="3">
-        <f t="shared" ref="AJ21:AL21" si="27">AJ19*0.8</f>
+        <f t="shared" ref="AJ21:AL21" si="28">AJ19*0.8</f>
         <v>1779.7296000000003</v>
       </c>
       <c r="AK21" s="3">
@@ -2541,48 +2539,48 @@
         <v>2368.5819999999994</v>
       </c>
       <c r="AL21" s="3">
-        <f t="shared" si="27"/>
-        <v>3553.4188320000003</v>
+        <f t="shared" si="28"/>
+        <v>3582.4736000000007</v>
       </c>
       <c r="AM21" s="3">
-        <f t="shared" ref="AM21" si="28">AM19*0.8</f>
-        <v>5685.4701312000007</v>
+        <f t="shared" ref="AM21" si="29">AM19*0.8</f>
+        <v>5731.9577600000011</v>
       </c>
       <c r="AN21" s="3">
-        <f t="shared" ref="AN21:AO21" si="29">AN19*0.8</f>
-        <v>8528.2051968000014</v>
+        <f t="shared" ref="AN21:AO21" si="30">AN19*0.8</f>
+        <v>8597.9366400000017</v>
       </c>
       <c r="AO21" s="3">
-        <f t="shared" si="29"/>
-        <v>11939.487275520001</v>
+        <f t="shared" si="30"/>
+        <v>12037.111296000003</v>
       </c>
       <c r="AP21" s="3">
-        <f t="shared" ref="AP21:AQ21" si="30">AP19*0.8</f>
-        <v>16118.307821952003</v>
+        <f t="shared" ref="AP21:AQ21" si="31">AP19*0.8</f>
+        <v>16250.100249600004</v>
       </c>
       <c r="AQ21" s="3">
-        <f t="shared" si="30"/>
-        <v>20953.800168537604</v>
+        <f t="shared" si="31"/>
+        <v>21125.130324480007</v>
       </c>
       <c r="AR21" s="3">
-        <f t="shared" ref="AR21:AV21" si="31">AR19*0.8</f>
-        <v>26192.250210672006</v>
+        <f t="shared" ref="AR21:AV21" si="32">AR19*0.8</f>
+        <v>26406.412905600006</v>
       </c>
       <c r="AS21" s="3">
-        <f t="shared" si="31"/>
-        <v>31430.700252806404</v>
+        <f t="shared" si="32"/>
+        <v>31687.695486720007</v>
       </c>
       <c r="AT21" s="3">
-        <f t="shared" si="31"/>
-        <v>37716.84030336768</v>
+        <f t="shared" si="32"/>
+        <v>38025.234584064012</v>
       </c>
       <c r="AU21" s="3">
-        <f t="shared" si="31"/>
-        <v>45260.208364041217</v>
+        <f t="shared" si="32"/>
+        <v>45630.281500876808</v>
       </c>
       <c r="AV21" s="3">
-        <f t="shared" si="31"/>
-        <v>54312.250036849458</v>
+        <f t="shared" si="32"/>
+        <v>54756.33780105217</v>
       </c>
     </row>
     <row r="22" spans="2:122" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2618,7 +2616,7 @@
         <v>168.875</v>
       </c>
       <c r="M22" s="4">
-        <f t="shared" ref="M22" si="32">L22+1</f>
+        <f t="shared" ref="M22" si="33">L22+1</f>
         <v>169.875</v>
       </c>
       <c r="N22" s="4">
@@ -2667,7 +2665,7 @@
         <v>274.63600000000002</v>
       </c>
       <c r="Z22" s="3">
-        <f t="shared" ref="Z22" si="33">+V22*1.24</f>
+        <f t="shared" ref="Z22" si="34">+V22*1.24</f>
         <v>236.02408000000003</v>
       </c>
       <c r="AG22" s="3">
@@ -2681,55 +2679,55 @@
         <v>675.96320000000003</v>
       </c>
       <c r="AJ22" s="3">
-        <f t="shared" ref="AJ22:AL22" si="34">AI22*1.1</f>
+        <f t="shared" ref="AJ22:AL22" si="35">AI22*1.1</f>
         <v>743.55952000000013</v>
       </c>
       <c r="AK22" s="3">
-        <f t="shared" ref="AK22:AK24" si="35">SUM(S22:V22)</f>
+        <f t="shared" ref="AK22:AK24" si="36">SUM(S22:V22)</f>
         <v>648.6339999999999</v>
       </c>
       <c r="AL22" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>713.49739999999997</v>
       </c>
       <c r="AM22" s="3">
-        <f t="shared" ref="AM22" si="36">AL22*1.1</f>
+        <f t="shared" ref="AM22" si="37">AL22*1.1</f>
         <v>784.84714000000008</v>
       </c>
       <c r="AN22" s="3">
-        <f t="shared" ref="AN22:AO22" si="37">AM22*1.1</f>
+        <f t="shared" ref="AN22:AO22" si="38">AM22*1.1</f>
         <v>863.33185400000013</v>
       </c>
       <c r="AO22" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>949.66503940000018</v>
       </c>
       <c r="AP22" s="3">
-        <f t="shared" ref="AP22:AP24" si="38">AO22*1.1</f>
+        <f t="shared" ref="AP22:AP24" si="39">AO22*1.1</f>
         <v>1044.6315433400002</v>
       </c>
       <c r="AQ22" s="3">
-        <f t="shared" ref="AQ22:AQ24" si="39">AP22*1.1</f>
+        <f t="shared" ref="AQ22:AQ24" si="40">AP22*1.1</f>
         <v>1149.0946976740004</v>
       </c>
       <c r="AR22" s="3">
-        <f t="shared" ref="AR22:AR24" si="40">AQ22*1.1</f>
+        <f t="shared" ref="AR22:AR24" si="41">AQ22*1.1</f>
         <v>1264.0041674414006</v>
       </c>
       <c r="AS22" s="3">
-        <f t="shared" ref="AS22:AS24" si="41">AR22*1.1</f>
+        <f t="shared" ref="AS22:AS24" si="42">AR22*1.1</f>
         <v>1390.4045841855407</v>
       </c>
       <c r="AT22" s="3">
-        <f t="shared" ref="AT22:AT24" si="42">AS22*1.1</f>
+        <f t="shared" ref="AT22:AT24" si="43">AS22*1.1</f>
         <v>1529.4450426040949</v>
       </c>
       <c r="AU22" s="3">
-        <f t="shared" ref="AU22:AU24" si="43">AT22*1.1</f>
+        <f t="shared" ref="AU22:AU24" si="44">AT22*1.1</f>
         <v>1682.3895468645044</v>
       </c>
       <c r="AV22" s="3">
-        <f t="shared" ref="AV22:AV24" si="44">AU22*1.1</f>
+        <f t="shared" ref="AV22:AV24" si="45">AU22*1.1</f>
         <v>1850.628501550955</v>
       </c>
     </row>
@@ -2766,7 +2764,7 @@
         <v>88.171000000000006</v>
       </c>
       <c r="M23" s="4">
-        <f t="shared" ref="M23" si="45">L23+1</f>
+        <f t="shared" ref="M23" si="46">L23+1</f>
         <v>89.171000000000006</v>
       </c>
       <c r="N23" s="4">
@@ -2815,7 +2813,7 @@
         <v>144.191</v>
       </c>
       <c r="Z23" s="3">
-        <f t="shared" ref="Z23" si="46">+V23*1.2</f>
+        <f t="shared" ref="Z23" si="47">+V23*1.2</f>
         <v>112.76280000000001</v>
       </c>
       <c r="AG23" s="3">
@@ -2825,59 +2823,59 @@
         <v>387.48700000000002</v>
       </c>
       <c r="AI23" s="3">
-        <f t="shared" ref="AI23:AL23" si="47">AH23*1.1</f>
+        <f t="shared" ref="AI23:AL23" si="48">AH23*1.1</f>
         <v>426.23570000000007</v>
       </c>
       <c r="AJ23" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>468.85927000000009</v>
       </c>
       <c r="AK23" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>342.81300000000005</v>
       </c>
       <c r="AL23" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>377.09430000000009</v>
       </c>
       <c r="AM23" s="3">
-        <f t="shared" ref="AM23" si="48">AL23*1.1</f>
+        <f t="shared" ref="AM23" si="49">AL23*1.1</f>
         <v>414.80373000000014</v>
       </c>
       <c r="AN23" s="3">
-        <f t="shared" ref="AN23:AO23" si="49">AM23*1.1</f>
+        <f t="shared" ref="AN23:AO23" si="50">AM23*1.1</f>
         <v>456.28410300000019</v>
       </c>
       <c r="AO23" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>501.91251330000023</v>
       </c>
       <c r="AP23" s="3">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>552.10376463000034</v>
       </c>
       <c r="AQ23" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>607.31414109300044</v>
       </c>
       <c r="AR23" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>668.04555520230053</v>
       </c>
       <c r="AS23" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>734.85011072253064</v>
       </c>
       <c r="AT23" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>808.33512179478373</v>
       </c>
       <c r="AU23" s="3">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>889.16863397426221</v>
       </c>
       <c r="AV23" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>978.08549737168846</v>
       </c>
     </row>
@@ -2914,7 +2912,7 @@
         <v>155.48500000000001</v>
       </c>
       <c r="M24" s="4">
-        <f t="shared" ref="M24" si="50">L24+1</f>
+        <f t="shared" ref="M24" si="51">L24+1</f>
         <v>156.48500000000001</v>
       </c>
       <c r="N24" s="4">
@@ -2963,7 +2961,7 @@
         <v>161.702</v>
       </c>
       <c r="Z24" s="3">
-        <f t="shared" ref="Z24" si="51">+V24*1.3</f>
+        <f t="shared" ref="Z24" si="52">+V24*1.3</f>
         <v>141.6454</v>
       </c>
       <c r="AG24" s="3">
@@ -2973,59 +2971,59 @@
         <v>611.53200000000004</v>
       </c>
       <c r="AI24" s="3">
-        <f t="shared" ref="AI24:AL24" si="52">AH24*1.1</f>
+        <f t="shared" ref="AI24:AL24" si="53">AH24*1.1</f>
         <v>672.68520000000012</v>
       </c>
       <c r="AJ24" s="3">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>739.9537200000002</v>
       </c>
       <c r="AK24" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>425.09399999999994</v>
       </c>
       <c r="AL24" s="3">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>467.60339999999997</v>
       </c>
       <c r="AM24" s="3">
-        <f t="shared" ref="AM24" si="53">AL24*1.1</f>
+        <f t="shared" ref="AM24" si="54">AL24*1.1</f>
         <v>514.36374000000001</v>
       </c>
       <c r="AN24" s="3">
-        <f t="shared" ref="AN24:AO24" si="54">AM24*1.1</f>
+        <f t="shared" ref="AN24:AO24" si="55">AM24*1.1</f>
         <v>565.80011400000001</v>
       </c>
       <c r="AO24" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>622.38012540000011</v>
       </c>
       <c r="AP24" s="3">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>684.61813794000022</v>
       </c>
       <c r="AQ24" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>753.07995173400036</v>
       </c>
       <c r="AR24" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>828.38794690740042</v>
       </c>
       <c r="AS24" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>911.22674159814051</v>
       </c>
       <c r="AT24" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1002.3494157579546</v>
       </c>
       <c r="AU24" s="3">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1102.5843573337502</v>
       </c>
       <c r="AV24" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1212.8427930671253</v>
       </c>
     </row>
@@ -3035,95 +3033,95 @@
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4">
-        <f t="shared" ref="D25:L25" si="55">SUM(D22:D24)</f>
+        <f t="shared" ref="D25:L25" si="56">SUM(D22:D24)</f>
         <v>282.62400000000002</v>
       </c>
       <c r="E25" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>987.803</v>
       </c>
       <c r="F25" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>408.15999999999997</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>381.137</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>430.86400000000003</v>
       </c>
       <c r="I25" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>397.28300000000002</v>
       </c>
       <c r="J25" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>404.24700000000001</v>
       </c>
       <c r="K25" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>391.39300000000003</v>
       </c>
       <c r="L25" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>412.53100000000001</v>
       </c>
       <c r="M25" s="4">
-        <f t="shared" ref="M25:N25" si="56">SUM(M22:M24)</f>
+        <f t="shared" ref="M25:N25" si="57">SUM(M22:M24)</f>
         <v>415.53100000000001</v>
       </c>
       <c r="N25" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>422.13900000000001</v>
       </c>
       <c r="O25" s="4">
-        <f t="shared" ref="O25:W25" si="57">+O22+O23+O24</f>
+        <f t="shared" ref="O25:W25" si="58">+O22+O23+O24</f>
         <v>307.88900000000001</v>
       </c>
       <c r="P25" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>310.14700000000005</v>
       </c>
       <c r="Q25" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>303.68799999999999</v>
       </c>
       <c r="R25" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>312.30900000000003</v>
       </c>
       <c r="S25" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>321.96600000000001</v>
       </c>
       <c r="T25" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>364.87100000000004</v>
       </c>
       <c r="U25" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>336.43499999999995</v>
       </c>
       <c r="V25" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>393.26900000000001</v>
       </c>
       <c r="W25" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>394.51400000000001</v>
       </c>
       <c r="X25" s="4">
-        <f t="shared" ref="X25:Z25" si="58">+X22+X23+X24</f>
+        <f t="shared" ref="X25:Z25" si="59">+X22+X23+X24</f>
         <v>541.44600000000003</v>
       </c>
       <c r="Y25" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>580.529</v>
       </c>
       <c r="Z25" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>490.43228000000005</v>
       </c>
       <c r="AA25" s="4"/>
@@ -3135,63 +3133,63 @@
         <v>1913.8049999999998</v>
       </c>
       <c r="AH25" s="3">
-        <f t="shared" ref="AH25" si="59">SUM(AH22:AH24)</f>
+        <f t="shared" ref="AH25" si="60">SUM(AH22:AH24)</f>
         <v>1613.5309999999999</v>
       </c>
       <c r="AI25" s="3">
-        <f t="shared" ref="AI25" si="60">SUM(AI22:AI24)</f>
+        <f t="shared" ref="AI25" si="61">SUM(AI22:AI24)</f>
         <v>1774.8841000000002</v>
       </c>
       <c r="AJ25" s="3">
-        <f t="shared" ref="AJ25" si="61">SUM(AJ22:AJ24)</f>
+        <f t="shared" ref="AJ25" si="62">SUM(AJ22:AJ24)</f>
         <v>1952.3725100000004</v>
       </c>
       <c r="AK25" s="3">
-        <f t="shared" ref="AK25" si="62">SUM(AK22:AK24)</f>
+        <f t="shared" ref="AK25" si="63">SUM(AK22:AK24)</f>
         <v>1416.5409999999997</v>
       </c>
       <c r="AL25" s="3">
-        <f t="shared" ref="AL25" si="63">SUM(AL22:AL24)</f>
+        <f t="shared" ref="AL25" si="64">SUM(AL22:AL24)</f>
         <v>1558.1950999999999</v>
       </c>
       <c r="AM25" s="3">
-        <f t="shared" ref="AM25" si="64">SUM(AM22:AM24)</f>
+        <f t="shared" ref="AM25" si="65">SUM(AM22:AM24)</f>
         <v>1714.0146100000002</v>
       </c>
       <c r="AN25" s="3">
-        <f t="shared" ref="AN25" si="65">SUM(AN22:AN24)</f>
+        <f t="shared" ref="AN25" si="66">SUM(AN22:AN24)</f>
         <v>1885.4160710000006</v>
       </c>
       <c r="AO25" s="3">
-        <f t="shared" ref="AO25:AQ25" si="66">SUM(AO22:AO24)</f>
+        <f t="shared" ref="AO25:AQ25" si="67">SUM(AO22:AO24)</f>
         <v>2073.9576781000005</v>
       </c>
       <c r="AP25" s="3">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>2281.353445910001</v>
       </c>
       <c r="AQ25" s="3">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>2509.4887905010009</v>
       </c>
       <c r="AR25" s="3">
-        <f t="shared" ref="AR25:AV25" si="67">SUM(AR22:AR24)</f>
+        <f t="shared" ref="AR25:AV25" si="68">SUM(AR22:AR24)</f>
         <v>2760.4376695511014</v>
       </c>
       <c r="AS25" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>3036.481436506212</v>
       </c>
       <c r="AT25" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>3340.1295801568331</v>
       </c>
       <c r="AU25" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>3674.1425381725167</v>
       </c>
       <c r="AV25" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>4041.5567919897685</v>
       </c>
     </row>
@@ -3201,96 +3199,96 @@
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4">
-        <f t="shared" ref="D26:L26" si="68">D21-D25</f>
+        <f t="shared" ref="D26:L26" si="69">D21-D25</f>
         <v>-99.14500000000001</v>
       </c>
       <c r="E26" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-847.77700000000004</v>
       </c>
       <c r="F26" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-156.57199999999995</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-114.01400000000001</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-146.14800000000002</v>
       </c>
       <c r="I26" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-91.941000000000031</v>
       </c>
       <c r="J26" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-58.942999999999984</v>
       </c>
       <c r="K26" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-39.439000000000021</v>
       </c>
       <c r="L26" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-41.745000000000005</v>
       </c>
       <c r="M26" s="4">
-        <f t="shared" ref="M26:N26" si="69">M21-M25</f>
+        <f t="shared" ref="M26:N26" si="70">M21-M25</f>
         <v>-33.226999999999975</v>
       </c>
       <c r="N26" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-17.826000000000022</v>
       </c>
       <c r="O26" s="4">
-        <f t="shared" ref="O26:W26" si="70">+O21-O25</f>
+        <f t="shared" ref="O26:W26" si="71">+O21-O25</f>
         <v>118.82900000000006</v>
       </c>
       <c r="P26" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>124.27499999999998</v>
       </c>
       <c r="Q26" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>154.363</v>
       </c>
       <c r="R26" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>198.05199999999996</v>
       </c>
       <c r="S26" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>206.53199999999993</v>
       </c>
       <c r="T26" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>197.10300000000001</v>
       </c>
       <c r="U26" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>255.56500000000005</v>
       </c>
       <c r="V26" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>292.84100000000001</v>
       </c>
       <c r="W26" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>330.53200000000004</v>
       </c>
       <c r="X26" s="4">
-        <f t="shared" ref="X26:Z26" si="71">+X21-X25</f>
+        <f t="shared" ref="X26:Z26" si="72">+X21-X25</f>
         <v>269.62</v>
       </c>
       <c r="Y26" s="4">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>393.25600000000009</v>
       </c>
       <c r="Z26" s="4">
-        <f t="shared" si="71"/>
-        <v>649.72339820000002</v>
+        <f t="shared" si="72"/>
+        <v>679.86771999999996</v>
       </c>
       <c r="AA26" s="4"/>
       <c r="AB26" s="4"/>
@@ -3301,64 +3299,64 @@
         <v>-1173.6789999999999</v>
       </c>
       <c r="AH26" s="3">
-        <f t="shared" ref="AH26" si="72">AH21-AH25</f>
+        <f t="shared" ref="AH26" si="73">AH21-AH25</f>
         <v>-411.04600000000005</v>
       </c>
       <c r="AI26" s="3">
-        <f t="shared" ref="AI26" si="73">AI21-AI25</f>
+        <f t="shared" ref="AI26" si="74">AI21-AI25</f>
         <v>-250.18730000000028</v>
       </c>
       <c r="AJ26" s="3">
-        <f t="shared" ref="AJ26" si="74">AJ21-AJ25</f>
+        <f t="shared" ref="AJ26" si="75">AJ21-AJ25</f>
         <v>-172.64291000000003</v>
       </c>
       <c r="AK26" s="3">
-        <f t="shared" ref="AK26" si="75">AK21-AK25</f>
+        <f t="shared" ref="AK26" si="76">AK21-AK25</f>
         <v>952.04099999999971</v>
       </c>
       <c r="AL26" s="3">
-        <f t="shared" ref="AL26" si="76">AL21-AL25</f>
-        <v>1995.2237320000004</v>
+        <f t="shared" ref="AL26" si="77">AL21-AL25</f>
+        <v>2024.2785000000008</v>
       </c>
       <c r="AM26" s="3">
-        <f t="shared" ref="AM26" si="77">AM21-AM25</f>
-        <v>3971.4555212000005</v>
+        <f t="shared" ref="AM26" si="78">AM21-AM25</f>
+        <v>4017.943150000001</v>
       </c>
       <c r="AN26" s="3">
-        <f t="shared" ref="AN26" si="78">AN21-AN25</f>
-        <v>6642.7891258000009</v>
+        <f t="shared" ref="AN26" si="79">AN21-AN25</f>
+        <v>6712.5205690000012</v>
       </c>
       <c r="AO26" s="3">
-        <f t="shared" ref="AO26:AQ26" si="79">AO21-AO25</f>
-        <v>9865.5295974200017</v>
+        <f t="shared" ref="AO26:AQ26" si="80">AO21-AO25</f>
+        <v>9963.1536179000032</v>
       </c>
       <c r="AP26" s="3">
-        <f t="shared" si="79"/>
-        <v>13836.954376042002</v>
+        <f t="shared" si="80"/>
+        <v>13968.746803690003</v>
       </c>
       <c r="AQ26" s="3">
-        <f t="shared" si="79"/>
-        <v>18444.311378036604</v>
+        <f t="shared" si="80"/>
+        <v>18615.641533979007</v>
       </c>
       <c r="AR26" s="3">
-        <f t="shared" ref="AR26:AV26" si="80">AR21-AR25</f>
-        <v>23431.812541120904</v>
+        <f t="shared" ref="AR26:AV26" si="81">AR21-AR25</f>
+        <v>23645.975236048904</v>
       </c>
       <c r="AS26" s="3">
-        <f t="shared" si="80"/>
-        <v>28394.218816300192</v>
+        <f t="shared" si="81"/>
+        <v>28651.214050213795</v>
       </c>
       <c r="AT26" s="3">
-        <f t="shared" si="80"/>
-        <v>34376.710723210846</v>
+        <f t="shared" si="81"/>
+        <v>34685.105003907178</v>
       </c>
       <c r="AU26" s="3">
-        <f t="shared" si="80"/>
-        <v>41586.065825868704</v>
+        <f t="shared" si="81"/>
+        <v>41956.138962704295</v>
       </c>
       <c r="AV26" s="3">
-        <f t="shared" si="80"/>
-        <v>50270.693244859693</v>
+        <f t="shared" si="81"/>
+        <v>50714.781009062404</v>
       </c>
     </row>
     <row r="27" spans="2:122" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3468,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3">
-        <f t="shared" ref="AK27" si="81">SUM(S27:V27)</f>
+        <f t="shared" ref="AK27" si="82">SUM(S27:V27)</f>
         <v>164.00200000000001</v>
       </c>
       <c r="AL27" s="3">
@@ -3476,44 +3474,44 @@
         <v>522.99869999999999</v>
       </c>
       <c r="AM27" s="3">
-        <f t="shared" ref="AM27:AV27" si="82">+AL41*$AY$39</f>
-        <v>749.63871888000006</v>
+        <f t="shared" ref="AM27:AV27" si="83">+AL41*$AY$39</f>
+        <v>752.25364800000011</v>
       </c>
       <c r="AN27" s="3">
-        <f t="shared" si="82"/>
-        <v>1174.5372004872002</v>
+        <f t="shared" si="83"/>
+        <v>1181.5713598200002</v>
       </c>
       <c r="AO27" s="3">
-        <f t="shared" si="82"/>
-        <v>1878.0965698530483</v>
+        <f t="shared" si="83"/>
+        <v>1892.0396334138004</v>
       </c>
       <c r="AP27" s="3">
-        <f t="shared" si="82"/>
-        <v>2935.0229249076228</v>
+        <f t="shared" si="83"/>
+        <v>2959.0070260320426</v>
       </c>
       <c r="AQ27" s="3">
-        <f t="shared" si="82"/>
-        <v>4444.500881993089</v>
+        <f t="shared" si="83"/>
+        <v>4482.5048707070264</v>
       </c>
       <c r="AR27" s="3">
-        <f t="shared" si="82"/>
-        <v>6504.4939853957612</v>
+        <f t="shared" si="83"/>
+        <v>6561.338047128771</v>
       </c>
       <c r="AS27" s="3">
-        <f t="shared" si="82"/>
-        <v>9198.7615727822613</v>
+        <f t="shared" si="83"/>
+        <v>9279.9962426147613</v>
       </c>
       <c r="AT27" s="3">
-        <f t="shared" si="82"/>
-        <v>12582.129807799683</v>
+        <f t="shared" si="83"/>
+        <v>12693.805168969333</v>
       </c>
       <c r="AU27" s="3">
-        <f t="shared" si="82"/>
-        <v>16808.42545559063</v>
+        <f t="shared" si="83"/>
+        <v>16957.907084528219</v>
       </c>
       <c r="AV27" s="3">
-        <f t="shared" si="82"/>
-        <v>22063.929670921971</v>
+        <f t="shared" si="83"/>
+        <v>22260.171228779145</v>
       </c>
     </row>
     <row r="28" spans="2:122" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3522,164 +3520,164 @@
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4">
-        <f t="shared" ref="D28:L28" si="83">D26-D27</f>
+        <f t="shared" ref="D28:L28" si="84">D26-D27</f>
         <v>-94.050000000000011</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-846.18600000000004</v>
       </c>
       <c r="F28" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-155.12599999999995</v>
       </c>
       <c r="G28" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-112.55000000000001</v>
       </c>
       <c r="H28" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-145.93000000000004</v>
       </c>
       <c r="I28" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-91.711000000000027</v>
       </c>
       <c r="J28" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-58.821999999999981</v>
       </c>
       <c r="K28" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-39.392000000000024</v>
       </c>
       <c r="L28" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-42.547000000000004</v>
       </c>
       <c r="M28" s="4">
-        <f t="shared" ref="M28" si="84">M26-M27</f>
+        <f t="shared" ref="M28" si="85">M26-M27</f>
         <v>-33.226999999999975</v>
       </c>
       <c r="N28" s="4">
-        <f t="shared" ref="N28:Z28" si="85">+N26+N27</f>
+        <f t="shared" ref="N28:Z28" si="86">+N26+N27</f>
         <v>37.848999999999975</v>
       </c>
       <c r="O28" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>135.54600000000008</v>
       </c>
       <c r="P28" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>144.24399999999997</v>
       </c>
       <c r="Q28" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>194.34899999999999</v>
       </c>
       <c r="R28" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>238.50499999999997</v>
       </c>
       <c r="S28" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>236.37699999999992</v>
       </c>
       <c r="T28" s="4">
-        <f t="shared" ref="T28" si="86">+T26+T27</f>
+        <f t="shared" ref="T28" si="87">+T26+T27</f>
         <v>232.52300000000002</v>
       </c>
       <c r="U28" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>299.57500000000005</v>
       </c>
       <c r="V28" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>347.56799999999998</v>
       </c>
       <c r="W28" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>380.97300000000007</v>
       </c>
       <c r="X28" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>325.875</v>
       </c>
       <c r="Y28" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>453.01800000000009</v>
       </c>
       <c r="Z28" s="4">
-        <f t="shared" si="85"/>
-        <v>709.48539819999996</v>
+        <f t="shared" si="86"/>
+        <v>739.62971999999991</v>
       </c>
       <c r="AA28" s="4"/>
       <c r="AB28" s="4"/>
       <c r="AC28" s="4"/>
       <c r="AD28" s="4"/>
       <c r="AG28" s="3">
-        <f t="shared" ref="AG28:AL28" si="87">AG26+AG27</f>
+        <f t="shared" ref="AG28:AL28" si="88">AG26+AG27</f>
         <v>-1183.1379999999999</v>
       </c>
       <c r="AH28" s="3">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>-413.07900000000006</v>
       </c>
       <c r="AI28" s="3">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>-250.18730000000028</v>
       </c>
       <c r="AJ28" s="3">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>-172.64291000000003</v>
       </c>
       <c r="AK28" s="3">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>1116.0429999999997</v>
       </c>
       <c r="AL28" s="3">
-        <f t="shared" si="87"/>
-        <v>2518.2224320000005</v>
+        <f t="shared" si="88"/>
+        <v>2547.2772000000009</v>
       </c>
       <c r="AM28" s="3">
-        <f t="shared" ref="AM28" si="88">AM26+AM27</f>
-        <v>4721.0942400800004</v>
+        <f t="shared" ref="AM28" si="89">AM26+AM27</f>
+        <v>4770.1967980000009</v>
       </c>
       <c r="AN28" s="3">
-        <f t="shared" ref="AN28" si="89">AN26+AN27</f>
-        <v>7817.3263262872006</v>
+        <f t="shared" ref="AN28" si="90">AN26+AN27</f>
+        <v>7894.0919288200012</v>
       </c>
       <c r="AO28" s="3">
-        <f t="shared" ref="AO28:AQ28" si="90">AO26+AO27</f>
-        <v>11743.626167273051</v>
+        <f t="shared" ref="AO28:AQ28" si="91">AO26+AO27</f>
+        <v>11855.193251313804</v>
       </c>
       <c r="AP28" s="3">
-        <f t="shared" si="90"/>
-        <v>16771.977300949624</v>
+        <f t="shared" si="91"/>
+        <v>16927.753829722045</v>
       </c>
       <c r="AQ28" s="3">
-        <f t="shared" si="90"/>
-        <v>22888.812260029692</v>
+        <f t="shared" si="91"/>
+        <v>23098.146404686035</v>
       </c>
       <c r="AR28" s="3">
-        <f t="shared" ref="AR28:AV28" si="91">AR26+AR27</f>
-        <v>29936.306526516666</v>
+        <f t="shared" ref="AR28:AV28" si="92">AR26+AR27</f>
+        <v>30207.313283177675</v>
       </c>
       <c r="AS28" s="3">
-        <f t="shared" si="91"/>
-        <v>37592.980389082455</v>
+        <f t="shared" si="92"/>
+        <v>37931.21029282856</v>
       </c>
       <c r="AT28" s="3">
-        <f t="shared" si="91"/>
-        <v>46958.84053101053</v>
+        <f t="shared" si="92"/>
+        <v>47378.910172876509</v>
       </c>
       <c r="AU28" s="3">
-        <f t="shared" si="91"/>
-        <v>58394.491281459334</v>
+        <f t="shared" si="92"/>
+        <v>58914.046047232514</v>
       </c>
       <c r="AV28" s="3">
-        <f t="shared" si="91"/>
-        <v>72334.622915781656</v>
+        <f t="shared" si="92"/>
+        <v>72974.952237841557</v>
       </c>
     </row>
     <row r="29" spans="2:122" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3764,7 +3762,7 @@
       </c>
       <c r="Z29" s="3">
         <f>+Z28*0.05</f>
-        <v>35.474269909999997</v>
+        <v>36.981485999999997</v>
       </c>
       <c r="AG29" s="3">
         <v>-12.635999999999999</v>
@@ -3779,52 +3777,52 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3">
-        <f t="shared" ref="AK29" si="92">SUM(S29:V29)</f>
+        <f t="shared" ref="AK29" si="93">SUM(S29:V29)</f>
         <v>29.056000000000001</v>
       </c>
       <c r="AL29" s="3">
         <f>AL28*0.1</f>
-        <v>251.82224320000006</v>
+        <v>254.72772000000009</v>
       </c>
       <c r="AM29" s="3">
-        <f t="shared" ref="AM29" si="93">AM28*0.1</f>
-        <v>472.10942400800008</v>
+        <f t="shared" ref="AM29" si="94">AM28*0.1</f>
+        <v>477.01967980000012</v>
       </c>
       <c r="AN29" s="3">
-        <f t="shared" ref="AN29" si="94">AN28*0.1</f>
-        <v>781.73263262872013</v>
+        <f t="shared" ref="AN29" si="95">AN28*0.1</f>
+        <v>789.40919288200018</v>
       </c>
       <c r="AO29" s="3">
-        <f t="shared" ref="AO29:AQ29" si="95">AO28*0.1</f>
-        <v>1174.3626167273051</v>
+        <f t="shared" ref="AO29:AQ29" si="96">AO28*0.1</f>
+        <v>1185.5193251313804</v>
       </c>
       <c r="AP29" s="3">
-        <f t="shared" si="95"/>
-        <v>1677.1977300949625</v>
+        <f t="shared" si="96"/>
+        <v>1692.7753829722046</v>
       </c>
       <c r="AQ29" s="3">
-        <f t="shared" si="95"/>
-        <v>2288.8812260029695</v>
+        <f t="shared" si="96"/>
+        <v>2309.8146404686036</v>
       </c>
       <c r="AR29" s="3">
-        <f t="shared" ref="AR29:AV29" si="96">AR28*0.1</f>
-        <v>2993.6306526516669</v>
+        <f t="shared" ref="AR29:AV29" si="97">AR28*0.1</f>
+        <v>3020.7313283177677</v>
       </c>
       <c r="AS29" s="3">
-        <f t="shared" si="96"/>
-        <v>3759.2980389082459</v>
+        <f t="shared" si="97"/>
+        <v>3793.1210292828564</v>
       </c>
       <c r="AT29" s="3">
-        <f t="shared" si="96"/>
-        <v>4695.8840531010528</v>
+        <f t="shared" si="97"/>
+        <v>4737.8910172876513</v>
       </c>
       <c r="AU29" s="3">
-        <f t="shared" si="96"/>
-        <v>5839.4491281459341</v>
+        <f t="shared" si="97"/>
+        <v>5891.4046047232514</v>
       </c>
       <c r="AV29" s="3">
-        <f t="shared" si="96"/>
-        <v>7233.4622915781656</v>
+        <f t="shared" si="97"/>
+        <v>7297.4952237841562</v>
       </c>
     </row>
     <row r="30" spans="2:122" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3833,47 +3831,47 @@
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4">
-        <f t="shared" ref="D30:L30" si="97">D28-D29</f>
+        <f t="shared" ref="D30:L30" si="98">D28-D29</f>
         <v>-94.993000000000009</v>
       </c>
       <c r="E30" s="4">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-837.64300000000003</v>
       </c>
       <c r="F30" s="4">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-147.53299999999996</v>
       </c>
       <c r="G30" s="4">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-115.65200000000002</v>
       </c>
       <c r="H30" s="4">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-140.26900000000003</v>
       </c>
       <c r="I30" s="4">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-93.149000000000029</v>
       </c>
       <c r="J30" s="4">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-91.827999999999975</v>
       </c>
       <c r="K30" s="4">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-41.415000000000028</v>
       </c>
       <c r="L30" s="4">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-45.135000000000005</v>
       </c>
       <c r="M30" s="4">
-        <f t="shared" ref="M30:N30" si="98">M28-M29</f>
+        <f t="shared" ref="M30:N30" si="99">M28-M29</f>
         <v>-33.226999999999975</v>
       </c>
       <c r="N30" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>30.877999999999975</v>
       </c>
       <c r="O30" s="4">
@@ -3897,19 +3895,19 @@
         <v>231.18099999999993</v>
       </c>
       <c r="T30" s="4">
-        <f t="shared" ref="T30:W30" si="99">+T28-T29</f>
+        <f t="shared" ref="T30:W30" si="100">+T28-T29</f>
         <v>225.89000000000001</v>
       </c>
       <c r="U30" s="4">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>285.95000000000005</v>
       </c>
       <c r="V30" s="4">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>343.96600000000001</v>
       </c>
       <c r="W30" s="4">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>375.37400000000008</v>
       </c>
       <c r="X30" s="3">
@@ -3922,7 +3920,7 @@
       </c>
       <c r="Z30" s="3">
         <f>+Z28-Z29</f>
-        <v>674.01112828999999</v>
+        <v>702.64823399999989</v>
       </c>
       <c r="AG30" s="3">
         <f>AG28-AG29</f>
@@ -3933,356 +3931,356 @@
         <v>-444.96400000000006</v>
       </c>
       <c r="AI30" s="3">
-        <f t="shared" ref="AI30:AL30" si="100">AI28-AI29</f>
+        <f t="shared" ref="AI30:AL30" si="101">AI28-AI29</f>
         <v>-250.18730000000028</v>
       </c>
       <c r="AJ30" s="3">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>-172.64291000000003</v>
       </c>
       <c r="AK30" s="3">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>1086.9869999999996</v>
       </c>
       <c r="AL30" s="3">
-        <f t="shared" si="100"/>
-        <v>2266.4001888000003</v>
+        <f t="shared" si="101"/>
+        <v>2292.5494800000006</v>
       </c>
       <c r="AM30" s="3">
-        <f t="shared" ref="AM30" si="101">AM28-AM29</f>
-        <v>4248.9848160720003</v>
+        <f t="shared" ref="AM30" si="102">AM28-AM29</f>
+        <v>4293.1771182000011</v>
       </c>
       <c r="AN30" s="3">
-        <f t="shared" ref="AN30" si="102">AN28-AN29</f>
-        <v>7035.5936936584803</v>
+        <f t="shared" ref="AN30" si="103">AN28-AN29</f>
+        <v>7104.6827359380013</v>
       </c>
       <c r="AO30" s="3">
-        <f t="shared" ref="AO30:AQ30" si="103">AO28-AO29</f>
-        <v>10569.263550545746</v>
+        <f t="shared" ref="AO30:AQ30" si="104">AO28-AO29</f>
+        <v>10669.673926182422</v>
       </c>
       <c r="AP30" s="3">
-        <f t="shared" si="103"/>
-        <v>15094.779570854662</v>
+        <f t="shared" si="104"/>
+        <v>15234.978446749841</v>
       </c>
       <c r="AQ30" s="3">
-        <f t="shared" si="103"/>
-        <v>20599.931034026722</v>
+        <f t="shared" si="104"/>
+        <v>20788.33176421743</v>
       </c>
       <c r="AR30" s="3">
-        <f t="shared" ref="AR30:AV30" si="104">AR28-AR29</f>
-        <v>26942.675873864999</v>
+        <f t="shared" ref="AR30:AV30" si="105">AR28-AR29</f>
+        <v>27186.581954859907</v>
       </c>
       <c r="AS30" s="3">
-        <f t="shared" si="104"/>
-        <v>33833.682350174211</v>
+        <f t="shared" si="105"/>
+        <v>34138.089263545706</v>
       </c>
       <c r="AT30" s="3">
-        <f t="shared" si="104"/>
-        <v>42262.95647790948</v>
+        <f t="shared" si="105"/>
+        <v>42641.01915558886</v>
       </c>
       <c r="AU30" s="3">
-        <f t="shared" si="104"/>
-        <v>52555.042153313399</v>
+        <f t="shared" si="105"/>
+        <v>53022.641442509266</v>
       </c>
       <c r="AV30" s="3">
-        <f t="shared" si="104"/>
-        <v>65101.16062420349</v>
+        <f t="shared" si="105"/>
+        <v>65677.457014057407</v>
       </c>
       <c r="AW30" s="3">
-        <f>+AV30*(1+$AY$35)</f>
-        <v>66403.18383668756</v>
+        <f t="shared" ref="AW30:CB30" si="106">+AV30*(1+$AY$35)</f>
+        <v>66991.006154338553</v>
       </c>
       <c r="AX30" s="3">
-        <f>+AW30*(1+$AY$35)</f>
-        <v>67731.247513421316</v>
+        <f t="shared" si="106"/>
+        <v>68330.826277425323</v>
       </c>
       <c r="AY30" s="3">
-        <f>+AX30*(1+$AY$35)</f>
-        <v>69085.872463689739</v>
+        <f t="shared" si="106"/>
+        <v>69697.442802973834</v>
       </c>
       <c r="AZ30" s="3">
-        <f>+AY30*(1+$AY$35)</f>
-        <v>70467.589912963536</v>
+        <f t="shared" si="106"/>
+        <v>71091.39165903331</v>
       </c>
       <c r="BA30" s="3">
-        <f>+AZ30*(1+$AY$35)</f>
-        <v>71876.941711222811</v>
+        <f t="shared" si="106"/>
+        <v>72513.219492213975</v>
       </c>
       <c r="BB30" s="3">
-        <f>+BA30*(1+$AY$35)</f>
-        <v>73314.480545447266</v>
+        <f t="shared" si="106"/>
+        <v>73963.483882058252</v>
       </c>
       <c r="BC30" s="3">
-        <f>+BB30*(1+$AY$35)</f>
-        <v>74780.770156356215</v>
+        <f t="shared" si="106"/>
+        <v>75442.753559699413</v>
       </c>
       <c r="BD30" s="3">
-        <f>+BC30*(1+$AY$35)</f>
-        <v>76276.385559483344</v>
+        <f t="shared" si="106"/>
+        <v>76951.608630893403</v>
       </c>
       <c r="BE30" s="3">
-        <f>+BD30*(1+$AY$35)</f>
-        <v>77801.913270673016</v>
+        <f t="shared" si="106"/>
+        <v>78490.640803511269</v>
       </c>
       <c r="BF30" s="3">
-        <f>+BE30*(1+$AY$35)</f>
-        <v>79357.951536086475</v>
+        <f t="shared" si="106"/>
+        <v>80060.453619581502</v>
       </c>
       <c r="BG30" s="3">
-        <f>+BF30*(1+$AY$35)</f>
-        <v>80945.110566808202</v>
+        <f t="shared" si="106"/>
+        <v>81661.662691973135</v>
       </c>
       <c r="BH30" s="3">
-        <f>+BG30*(1+$AY$35)</f>
-        <v>82564.012778144373</v>
+        <f t="shared" si="106"/>
+        <v>83294.895945812605</v>
       </c>
       <c r="BI30" s="3">
-        <f>+BH30*(1+$AY$35)</f>
-        <v>84215.293033707261</v>
+        <f t="shared" si="106"/>
+        <v>84960.793864728854</v>
       </c>
       <c r="BJ30" s="3">
-        <f>+BI30*(1+$AY$35)</f>
-        <v>85899.598894381401</v>
+        <f t="shared" si="106"/>
+        <v>86660.009742023438</v>
       </c>
       <c r="BK30" s="3">
-        <f>+BJ30*(1+$AY$35)</f>
-        <v>87617.590872269036</v>
+        <f t="shared" si="106"/>
+        <v>88393.209936863903</v>
       </c>
       <c r="BL30" s="3">
-        <f>+BK30*(1+$AY$35)</f>
-        <v>89369.942689714415</v>
+        <f t="shared" si="106"/>
+        <v>90161.074135601186</v>
       </c>
       <c r="BM30" s="3">
-        <f>+BL30*(1+$AY$35)</f>
-        <v>91157.341543508708</v>
+        <f t="shared" si="106"/>
+        <v>91964.295618313205</v>
       </c>
       <c r="BN30" s="3">
-        <f>+BM30*(1+$AY$35)</f>
-        <v>92980.488374378881</v>
+        <f t="shared" si="106"/>
+        <v>93803.581530679468</v>
       </c>
       <c r="BO30" s="3">
-        <f>+BN30*(1+$AY$35)</f>
-        <v>94840.09814186646</v>
+        <f t="shared" si="106"/>
+        <v>95679.653161293056</v>
       </c>
       <c r="BP30" s="3">
-        <f>+BO30*(1+$AY$35)</f>
-        <v>96736.900104703789</v>
+        <f t="shared" si="106"/>
+        <v>97593.246224518924</v>
       </c>
       <c r="BQ30" s="3">
-        <f>+BP30*(1+$AY$35)</f>
-        <v>98671.638106797865</v>
+        <f t="shared" si="106"/>
+        <v>99545.111149009303</v>
       </c>
       <c r="BR30" s="3">
-        <f>+BQ30*(1+$AY$35)</f>
-        <v>100645.07086893382</v>
+        <f t="shared" si="106"/>
+        <v>101536.01337198949</v>
       </c>
       <c r="BS30" s="3">
-        <f>+BR30*(1+$AY$35)</f>
-        <v>102657.97228631251</v>
+        <f t="shared" si="106"/>
+        <v>103566.73363942928</v>
       </c>
       <c r="BT30" s="3">
-        <f>+BS30*(1+$AY$35)</f>
-        <v>104711.13173203876</v>
+        <f t="shared" si="106"/>
+        <v>105638.06831221787</v>
       </c>
       <c r="BU30" s="3">
-        <f>+BT30*(1+$AY$35)</f>
-        <v>106805.35436667954</v>
+        <f t="shared" si="106"/>
+        <v>107750.82967846224</v>
       </c>
       <c r="BV30" s="3">
-        <f>+BU30*(1+$AY$35)</f>
-        <v>108941.46145401314</v>
+        <f t="shared" si="106"/>
+        <v>109905.84627203149</v>
       </c>
       <c r="BW30" s="3">
-        <f>+BV30*(1+$AY$35)</f>
-        <v>111120.29068309341</v>
+        <f t="shared" si="106"/>
+        <v>112103.96319747211</v>
       </c>
       <c r="BX30" s="3">
-        <f>+BW30*(1+$AY$35)</f>
-        <v>113342.69649675528</v>
+        <f t="shared" si="106"/>
+        <v>114346.04246142156</v>
       </c>
       <c r="BY30" s="3">
-        <f>+BX30*(1+$AY$35)</f>
-        <v>115609.55042669039</v>
+        <f t="shared" si="106"/>
+        <v>116632.96331065</v>
       </c>
       <c r="BZ30" s="3">
-        <f>+BY30*(1+$AY$35)</f>
-        <v>117921.7414352242</v>
+        <f t="shared" si="106"/>
+        <v>118965.622576863</v>
       </c>
       <c r="CA30" s="3">
-        <f>+BZ30*(1+$AY$35)</f>
-        <v>120280.17626392869</v>
+        <f t="shared" si="106"/>
+        <v>121344.93502840026</v>
       </c>
       <c r="CB30" s="3">
-        <f>+CA30*(1+$AY$35)</f>
-        <v>122685.77978920727</v>
+        <f t="shared" si="106"/>
+        <v>123771.83372896827</v>
       </c>
       <c r="CC30" s="3">
-        <f>+CB30*(1+$AY$35)</f>
-        <v>125139.49538499142</v>
+        <f t="shared" ref="CC30:DH30" si="107">+CB30*(1+$AY$35)</f>
+        <v>126247.27040354763</v>
       </c>
       <c r="CD30" s="3">
-        <f>+CC30*(1+$AY$35)</f>
-        <v>127642.28529269125</v>
+        <f t="shared" si="107"/>
+        <v>128772.21581161859</v>
       </c>
       <c r="CE30" s="3">
-        <f>+CD30*(1+$AY$35)</f>
-        <v>130195.13099854508</v>
+        <f t="shared" si="107"/>
+        <v>131347.66012785098</v>
       </c>
       <c r="CF30" s="3">
-        <f>+CE30*(1+$AY$35)</f>
-        <v>132799.03361851597</v>
+        <f t="shared" si="107"/>
+        <v>133974.613330408</v>
       </c>
       <c r="CG30" s="3">
-        <f>+CF30*(1+$AY$35)</f>
-        <v>135455.01429088629</v>
+        <f t="shared" si="107"/>
+        <v>136654.10559701617</v>
       </c>
       <c r="CH30" s="3">
-        <f>+CG30*(1+$AY$35)</f>
-        <v>138164.11457670401</v>
+        <f t="shared" si="107"/>
+        <v>139387.18770895648</v>
       </c>
       <c r="CI30" s="3">
-        <f>+CH30*(1+$AY$35)</f>
-        <v>140927.39686823811</v>
+        <f t="shared" si="107"/>
+        <v>142174.93146313561</v>
       </c>
       <c r="CJ30" s="3">
-        <f>+CI30*(1+$AY$35)</f>
-        <v>143745.94480560286</v>
+        <f t="shared" si="107"/>
+        <v>145018.43009239834</v>
       </c>
       <c r="CK30" s="3">
-        <f>+CJ30*(1+$AY$35)</f>
-        <v>146620.86370171493</v>
+        <f t="shared" si="107"/>
+        <v>147918.7986942463</v>
       </c>
       <c r="CL30" s="3">
-        <f>+CK30*(1+$AY$35)</f>
-        <v>149553.28097574922</v>
+        <f t="shared" si="107"/>
+        <v>150877.17466813122</v>
       </c>
       <c r="CM30" s="3">
-        <f>+CL30*(1+$AY$35)</f>
-        <v>152544.34659526421</v>
+        <f t="shared" si="107"/>
+        <v>153894.71816149386</v>
       </c>
       <c r="CN30" s="3">
-        <f>+CM30*(1+$AY$35)</f>
-        <v>155595.2335271695</v>
+        <f t="shared" si="107"/>
+        <v>156972.61252472375</v>
       </c>
       <c r="CO30" s="3">
-        <f>+CN30*(1+$AY$35)</f>
-        <v>158707.13819771289</v>
+        <f t="shared" si="107"/>
+        <v>160112.06477521823</v>
       </c>
       <c r="CP30" s="3">
-        <f>+CO30*(1+$AY$35)</f>
-        <v>161881.28096166716</v>
+        <f t="shared" si="107"/>
+        <v>163314.30607072258</v>
       </c>
       <c r="CQ30" s="3">
-        <f>+CP30*(1+$AY$35)</f>
-        <v>165118.90658090051</v>
+        <f t="shared" si="107"/>
+        <v>166580.59219213703</v>
       </c>
       <c r="CR30" s="3">
-        <f>+CQ30*(1+$AY$35)</f>
-        <v>168421.28471251854</v>
+        <f t="shared" si="107"/>
+        <v>169912.20403597978</v>
       </c>
       <c r="CS30" s="3">
-        <f>+CR30*(1+$AY$35)</f>
-        <v>171789.71040676892</v>
+        <f t="shared" si="107"/>
+        <v>173310.44811669938</v>
       </c>
       <c r="CT30" s="3">
-        <f>+CS30*(1+$AY$35)</f>
-        <v>175225.50461490429</v>
+        <f t="shared" si="107"/>
+        <v>176776.65707903338</v>
       </c>
       <c r="CU30" s="3">
-        <f>+CT30*(1+$AY$35)</f>
-        <v>178730.01470720238</v>
+        <f t="shared" si="107"/>
+        <v>180312.19022061405</v>
       </c>
       <c r="CV30" s="3">
-        <f>+CU30*(1+$AY$35)</f>
-        <v>182304.61500134642</v>
+        <f t="shared" si="107"/>
+        <v>183918.43402502633</v>
       </c>
       <c r="CW30" s="3">
-        <f>+CV30*(1+$AY$35)</f>
-        <v>185950.70730137336</v>
+        <f t="shared" si="107"/>
+        <v>187596.80270552688</v>
       </c>
       <c r="CX30" s="3">
-        <f>+CW30*(1+$AY$35)</f>
-        <v>189669.72144740084</v>
+        <f t="shared" si="107"/>
+        <v>191348.7387596374</v>
       </c>
       <c r="CY30" s="3">
-        <f>+CX30*(1+$AY$35)</f>
-        <v>193463.11587634886</v>
+        <f t="shared" si="107"/>
+        <v>195175.71353483017</v>
       </c>
       <c r="CZ30" s="3">
-        <f>+CY30*(1+$AY$35)</f>
-        <v>197332.37819387583</v>
+        <f t="shared" si="107"/>
+        <v>199079.22780552678</v>
       </c>
       <c r="DA30" s="3">
-        <f>+CZ30*(1+$AY$35)</f>
-        <v>201279.02575775335</v>
+        <f t="shared" si="107"/>
+        <v>203060.81236163733</v>
       </c>
       <c r="DB30" s="3">
-        <f>+DA30*(1+$AY$35)</f>
-        <v>205304.60627290842</v>
+        <f t="shared" si="107"/>
+        <v>207122.02860887008</v>
       </c>
       <c r="DC30" s="3">
-        <f>+DB30*(1+$AY$35)</f>
-        <v>209410.6983983666</v>
+        <f t="shared" si="107"/>
+        <v>211264.46918104749</v>
       </c>
       <c r="DD30" s="3">
-        <f>+DC30*(1+$AY$35)</f>
-        <v>213598.91236633394</v>
+        <f t="shared" si="107"/>
+        <v>215489.75856466845</v>
       </c>
       <c r="DE30" s="3">
-        <f>+DD30*(1+$AY$35)</f>
-        <v>217870.89061366062</v>
+        <f t="shared" si="107"/>
+        <v>219799.55373596182</v>
       </c>
       <c r="DF30" s="3">
-        <f>+DE30*(1+$AY$35)</f>
-        <v>222228.30842593385</v>
+        <f t="shared" si="107"/>
+        <v>224195.54481068105</v>
       </c>
       <c r="DG30" s="3">
-        <f>+DF30*(1+$AY$35)</f>
-        <v>226672.87459445253</v>
+        <f t="shared" si="107"/>
+        <v>228679.45570689469</v>
       </c>
       <c r="DH30" s="3">
-        <f>+DG30*(1+$AY$35)</f>
-        <v>231206.33208634157</v>
+        <f t="shared" si="107"/>
+        <v>233253.04482103258</v>
       </c>
       <c r="DI30" s="3">
-        <f>+DH30*(1+$AY$35)</f>
-        <v>235830.45872806842</v>
+        <f t="shared" ref="DI30:DR30" si="108">+DH30*(1+$AY$35)</f>
+        <v>237918.10571745323</v>
       </c>
       <c r="DJ30" s="3">
-        <f>+DI30*(1+$AY$35)</f>
-        <v>240547.06790262979</v>
+        <f t="shared" si="108"/>
+        <v>242676.46783180229</v>
       </c>
       <c r="DK30" s="3">
-        <f>+DJ30*(1+$AY$35)</f>
-        <v>245358.00926068239</v>
+        <f t="shared" si="108"/>
+        <v>247529.99718843834</v>
       </c>
       <c r="DL30" s="3">
-        <f>+DK30*(1+$AY$35)</f>
-        <v>250265.16944589606</v>
+        <f t="shared" si="108"/>
+        <v>252480.5971322071</v>
       </c>
       <c r="DM30" s="3">
-        <f>+DL30*(1+$AY$35)</f>
-        <v>255270.47283481399</v>
+        <f t="shared" si="108"/>
+        <v>257530.20907485124</v>
       </c>
       <c r="DN30" s="3">
-        <f>+DM30*(1+$AY$35)</f>
-        <v>260375.88229151026</v>
+        <f t="shared" si="108"/>
+        <v>262680.81325634825</v>
       </c>
       <c r="DO30" s="3">
-        <f>+DN30*(1+$AY$35)</f>
-        <v>265583.39993734047</v>
+        <f t="shared" si="108"/>
+        <v>267934.42952147522</v>
       </c>
       <c r="DP30" s="3">
-        <f>+DO30*(1+$AY$35)</f>
-        <v>270895.06793608726</v>
+        <f t="shared" si="108"/>
+        <v>273293.11811190471</v>
       </c>
       <c r="DQ30" s="3">
-        <f>+DP30*(1+$AY$35)</f>
-        <v>276312.96929480904</v>
+        <f t="shared" si="108"/>
+        <v>278758.98047414282</v>
       </c>
       <c r="DR30" s="3">
-        <f>+DQ30*(1+$AY$35)</f>
-        <v>281839.22868070524</v>
+        <f t="shared" si="108"/>
+        <v>284334.1600836257</v>
       </c>
     </row>
     <row r="31" spans="2:122" x14ac:dyDescent="0.25">
@@ -4290,47 +4288,47 @@
         <v>1</v>
       </c>
       <c r="D31" s="7">
-        <f t="shared" ref="D31:L31" si="105">D30/D32</f>
+        <f t="shared" ref="D31:L31" si="109">D30/D32</f>
         <v>-0.14827157237200492</v>
       </c>
       <c r="E31" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>-0.92510011463761044</v>
       </c>
       <c r="F31" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>-8.3658536308756248E-2</v>
       </c>
       <c r="G31" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>-6.3504649239659608E-2</v>
       </c>
       <c r="H31" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>-7.4035973706406522E-2</v>
       </c>
       <c r="I31" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>-4.7418670888492401E-2</v>
       </c>
       <c r="J31" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>-4.5645513091992884E-2</v>
       </c>
       <c r="K31" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>-2.0338288872945007E-2</v>
       </c>
       <c r="L31" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>-2.1965652114878394E-2</v>
       </c>
       <c r="M31" s="7">
-        <f t="shared" ref="M31:N31" si="106">M30/M32</f>
+        <f t="shared" ref="M31:N31" si="110">M30/M32</f>
         <v>-1.6170438081778302E-2</v>
       </c>
       <c r="N31" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>1.4011679273305783E-2</v>
       </c>
       <c r="O31" s="7">
@@ -4354,15 +4352,15 @@
         <v>9.6321122349961874E-2</v>
       </c>
       <c r="T31" s="7">
-        <f t="shared" ref="T31:Z31" si="107">+T30/T32</f>
+        <f t="shared" ref="T31:Z31" si="111">+T30/T32</f>
         <v>9.3548007699519944E-2</v>
       </c>
       <c r="U31" s="7">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.11625926120176991</v>
       </c>
       <c r="V31" s="7">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.13604748526566887</v>
       </c>
       <c r="W31" s="7">
@@ -4370,16 +4368,16 @@
         <v>0.14704299327253256</v>
       </c>
       <c r="X31" s="7">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.12574719693848249</v>
       </c>
       <c r="Y31" s="7">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>0.17473941651235275</v>
       </c>
       <c r="Z31" s="7">
-        <f t="shared" si="107"/>
-        <v>0.26215331993417496</v>
+        <f t="shared" si="111"/>
+        <v>0.273291581633546</v>
       </c>
       <c r="AA31" s="7"/>
       <c r="AB31" s="7"/>
@@ -4394,60 +4392,60 @@
         <v>-0.23131631712549852</v>
       </c>
       <c r="AI31" s="1">
-        <f t="shared" ref="AI31:AL31" si="108">AI30/AI32</f>
+        <f t="shared" ref="AI31:AL31" si="112">AI30/AI32</f>
         <v>-0.11985539971912569</v>
       </c>
       <c r="AJ31" s="1">
-        <f t="shared" si="108"/>
+        <f t="shared" si="112"/>
         <v>-7.5234388822408196E-2</v>
       </c>
       <c r="AK31" s="1">
-        <f t="shared" si="108"/>
+        <f t="shared" si="112"/>
         <v>0.44354727400317712</v>
       </c>
       <c r="AL31" s="1">
-        <f t="shared" si="108"/>
-        <v>0.92480924384792684</v>
+        <f t="shared" si="112"/>
+        <v>0.93547951573606847</v>
       </c>
       <c r="AM31" s="1">
-        <f t="shared" ref="AM31" si="109">AM30/AM32</f>
-        <v>1.7338069659063331</v>
+        <f t="shared" ref="AM31" si="113">AM30/AM32</f>
+        <v>1.7518397253972926</v>
       </c>
       <c r="AN31" s="1">
-        <f t="shared" ref="AN31" si="110">AN30/AN32</f>
-        <v>2.8708884317992434</v>
+        <f t="shared" ref="AN31" si="114">AN30/AN32</f>
+        <v>2.8990803571549022</v>
       </c>
       <c r="AO31" s="1">
-        <f t="shared" ref="AO31:AQ31" si="111">AO30/AO32</f>
-        <v>4.3128096619975294</v>
+        <f t="shared" ref="AO31:AQ31" si="115">AO30/AO32</f>
+        <v>4.3537823216478131</v>
       </c>
       <c r="AP31" s="1">
-        <f t="shared" si="111"/>
-        <v>6.1594557527656129</v>
+        <f t="shared" si="115"/>
+        <v>6.2166641915248775</v>
       </c>
       <c r="AQ31" s="1">
-        <f t="shared" si="111"/>
-        <v>8.4058440945439141</v>
+        <f t="shared" si="115"/>
+        <v>8.4827213987768957</v>
       </c>
       <c r="AR31" s="1">
-        <f t="shared" ref="AR31:AV31" si="112">AR30/AR32</f>
-        <v>10.99401413099144</v>
+        <f t="shared" ref="AR31:AV31" si="116">AR30/AR32</f>
+        <v>11.093540507422887</v>
       </c>
       <c r="AS31" s="1">
-        <f t="shared" si="112"/>
-        <v>13.805903452303646</v>
+        <f t="shared" si="116"/>
+        <v>13.930117317431424</v>
       </c>
       <c r="AT31" s="1">
-        <f t="shared" si="112"/>
-        <v>17.245486042695703</v>
+        <f t="shared" si="116"/>
+        <v>17.399755293465979</v>
       </c>
       <c r="AU31" s="1">
-        <f t="shared" si="112"/>
-        <v>21.44519270444286</v>
+        <f t="shared" si="116"/>
+        <v>21.635997553119662</v>
       </c>
       <c r="AV31" s="1">
-        <f t="shared" si="112"/>
-        <v>26.564662069839329</v>
+        <f t="shared" si="116"/>
+        <v>26.799820993301683</v>
       </c>
     </row>
     <row r="32" spans="2:122" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4483,7 +4481,7 @@
         <v>2054.799</v>
       </c>
       <c r="M32" s="4">
-        <f t="shared" ref="M32" si="113">L32</f>
+        <f t="shared" ref="M32" si="117">L32</f>
         <v>2054.799</v>
       </c>
       <c r="N32" s="4">
@@ -4549,43 +4547,43 @@
         <v>2450.6677500000001</v>
       </c>
       <c r="AM32" s="3">
-        <f t="shared" ref="AM32" si="114">AL32</f>
+        <f t="shared" ref="AM32" si="118">AL32</f>
         <v>2450.6677500000001</v>
       </c>
       <c r="AN32" s="3">
-        <f t="shared" ref="AN32:AO32" si="115">AM32</f>
+        <f t="shared" ref="AN32:AO32" si="119">AM32</f>
         <v>2450.6677500000001</v>
       </c>
       <c r="AO32" s="3">
-        <f t="shared" si="115"/>
+        <f t="shared" si="119"/>
         <v>2450.6677500000001</v>
       </c>
       <c r="AP32" s="3">
-        <f t="shared" ref="AP32" si="116">AO32</f>
+        <f t="shared" ref="AP32" si="120">AO32</f>
         <v>2450.6677500000001</v>
       </c>
       <c r="AQ32" s="3">
-        <f t="shared" ref="AQ32" si="117">AP32</f>
+        <f t="shared" ref="AQ32" si="121">AP32</f>
         <v>2450.6677500000001</v>
       </c>
       <c r="AR32" s="3">
-        <f t="shared" ref="AR32" si="118">AQ32</f>
+        <f t="shared" ref="AR32" si="122">AQ32</f>
         <v>2450.6677500000001</v>
       </c>
       <c r="AS32" s="3">
-        <f t="shared" ref="AS32" si="119">AR32</f>
+        <f t="shared" ref="AS32" si="123">AR32</f>
         <v>2450.6677500000001</v>
       </c>
       <c r="AT32" s="3">
-        <f t="shared" ref="AT32" si="120">AS32</f>
+        <f t="shared" ref="AT32" si="124">AS32</f>
         <v>2450.6677500000001</v>
       </c>
       <c r="AU32" s="3">
-        <f t="shared" ref="AU32" si="121">AT32</f>
+        <f t="shared" ref="AU32" si="125">AT32</f>
         <v>2450.6677500000001</v>
       </c>
       <c r="AV32" s="3">
-        <f t="shared" ref="AV32" si="122">AU32</f>
+        <f t="shared" ref="AV32" si="126">AU32</f>
         <v>2450.6677500000001</v>
       </c>
     </row>
@@ -4619,60 +4617,60 @@
         <v>0.25920424233711881</v>
       </c>
       <c r="M35" s="10">
-        <f t="shared" ref="M35:O35" si="123">M19/I19-1</f>
+        <f t="shared" ref="M35:O35" si="127">M19/I19-1</f>
         <v>0.21862775598884077</v>
       </c>
       <c r="N35" s="10">
-        <f t="shared" si="123"/>
+        <f t="shared" si="127"/>
         <v>0.17501218619113956</v>
       </c>
       <c r="O35" s="10">
-        <f t="shared" si="123"/>
+        <f t="shared" si="127"/>
         <v>0.1766052733574246</v>
       </c>
       <c r="P35" s="10">
-        <f t="shared" ref="P35:T35" si="124">P19/L19-1</f>
+        <f t="shared" ref="P35:T35" si="128">P19/L19-1</f>
         <v>0.12749624743662924</v>
       </c>
       <c r="Q35" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="128"/>
         <v>0.16798987193437687</v>
       </c>
       <c r="R35" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="128"/>
         <v>0.19538205039479051</v>
       </c>
       <c r="S35" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="128"/>
         <v>0.20783493847893864</v>
       </c>
       <c r="T35" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="128"/>
         <v>0.2715401909183468</v>
       </c>
       <c r="U35" s="10">
-        <f t="shared" ref="U35" si="125">U19/Q19-1</f>
+        <f t="shared" ref="U35" si="129">U19/Q19-1</f>
         <v>0.2998375015004684</v>
       </c>
       <c r="V35" s="10">
-        <f t="shared" ref="V35:Z35" si="126">V19/R19-1</f>
+        <f t="shared" ref="V35:Z35" si="130">V19/R19-1</f>
         <v>0.36105098684210524</v>
       </c>
       <c r="W35" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="130"/>
         <v>0.39200237097572588</v>
       </c>
       <c r="X35" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="130"/>
         <v>0.48053334591688368</v>
       </c>
       <c r="Y35" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="130"/>
         <v>0.62793377403117256</v>
       </c>
       <c r="Z35" s="10">
-        <f t="shared" si="126"/>
-        <v>0.66000000000000014</v>
+        <f t="shared" si="130"/>
+        <v>0.70388836993470849</v>
       </c>
       <c r="AA35" s="10"/>
       <c r="AB35" s="10"/>
@@ -4696,46 +4694,46 @@
       </c>
       <c r="AL35" s="12">
         <f>AL19/AK19-1</f>
-        <v>0.55008294867191077</v>
+        <v>0.56275730612418706</v>
       </c>
       <c r="AM35" s="12">
-        <f t="shared" ref="AM35" si="127">AM19/AL19-1</f>
+        <f t="shared" ref="AM35" si="131">AM19/AL19-1</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="AN35" s="12">
-        <f t="shared" ref="AN35:AO35" si="128">AN19/AM19-1</f>
-        <v>0.50000000000000022</v>
+        <f t="shared" ref="AN35:AO35" si="132">AN19/AM19-1</f>
+        <v>0.5</v>
       </c>
       <c r="AO35" s="12">
-        <f t="shared" si="128"/>
+        <f t="shared" si="132"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="AP35" s="12">
-        <f t="shared" ref="AP35" si="129">AP19/AO19-1</f>
+        <f t="shared" ref="AP35" si="133">AP19/AO19-1</f>
         <v>0.35000000000000009</v>
       </c>
       <c r="AQ35" s="12">
-        <f t="shared" ref="AQ35" si="130">AQ19/AP19-1</f>
+        <f t="shared" ref="AQ35" si="134">AQ19/AP19-1</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="AR35" s="12">
-        <f t="shared" ref="AR35" si="131">AR19/AQ19-1</f>
+        <f t="shared" ref="AR35" si="135">AR19/AQ19-1</f>
         <v>0.25</v>
       </c>
       <c r="AS35" s="12">
-        <f t="shared" ref="AS35" si="132">AS19/AR19-1</f>
+        <f t="shared" ref="AS35" si="136">AS19/AR19-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="AT35" s="12">
-        <f t="shared" ref="AT35" si="133">AT19/AS19-1</f>
+        <f t="shared" ref="AT35" si="137">AT19/AS19-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="AU35" s="12">
-        <f t="shared" ref="AU35" si="134">AU19/AT19-1</f>
+        <f t="shared" ref="AU35" si="138">AU19/AT19-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="AV35" s="12">
-        <f t="shared" ref="AV35" si="135">AV19/AU19-1</f>
+        <f t="shared" ref="AV35" si="139">AV19/AU19-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="AX35" s="11" t="s">
@@ -4750,95 +4748,95 @@
         <v>33</v>
       </c>
       <c r="D36" s="8">
-        <f t="shared" ref="D36:K36" si="136">D21/D19</f>
+        <f t="shared" ref="D36:K36" si="140">D21/D19</f>
         <v>0.72841211803611916</v>
       </c>
       <c r="E36" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="140"/>
         <v>0.48390619492269304</v>
       </c>
       <c r="F36" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="140"/>
         <v>0.78110844450791861</v>
       </c>
       <c r="G36" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="140"/>
         <v>0.78281472537906538</v>
       </c>
       <c r="H36" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="140"/>
         <v>0.75794506471587308</v>
       </c>
       <c r="I36" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="140"/>
         <v>0.77864366842961541</v>
       </c>
       <c r="J36" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="140"/>
         <v>0.79771384744043783</v>
       </c>
       <c r="K36" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="140"/>
         <v>0.78850337286073702</v>
       </c>
       <c r="L36" s="8">
-        <f t="shared" ref="L36:P36" si="137">L21/L19</f>
+        <f t="shared" ref="L36:P36" si="141">L21/L19</f>
         <v>0.78388617576795416</v>
       </c>
       <c r="M36" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="141"/>
         <v>0.8</v>
       </c>
       <c r="N36" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="141"/>
         <v>0.79491530089024498</v>
       </c>
       <c r="O36" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="141"/>
         <v>0.8125083303819981</v>
       </c>
       <c r="P36" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="141"/>
         <v>0.81456619608975533</v>
       </c>
       <c r="Q36" s="8">
-        <f t="shared" ref="Q36:R36" si="138">Q21/Q19</f>
+        <f t="shared" ref="Q36:R36" si="142">Q21/Q19</f>
         <v>0.82064608830100383</v>
       </c>
       <c r="R36" s="8">
-        <f t="shared" si="138"/>
+        <f t="shared" si="142"/>
         <v>0.83940953947368424</v>
       </c>
       <c r="S36" s="8">
-        <f t="shared" ref="S36:W36" si="139">S21/S19</f>
+        <f t="shared" ref="S36:W36" si="143">S21/S19</f>
         <v>0.83314888907806239</v>
       </c>
       <c r="T36" s="8">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.82870642085487534</v>
       </c>
       <c r="U36" s="8">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.81597097789711048</v>
       </c>
       <c r="V36" s="8">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.82911691453610126</v>
       </c>
       <c r="W36" s="8">
-        <f t="shared" si="139"/>
+        <f t="shared" si="143"/>
         <v>0.82111664779161952</v>
       </c>
       <c r="X36" s="8">
-        <f t="shared" ref="X36:Z36" si="140">X21/X19</f>
+        <f t="shared" ref="X36:Z36" si="144">X21/X19</f>
         <v>0.80783466135458171</v>
       </c>
       <c r="Y36" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="144"/>
         <v>0.82447853342499988</v>
       </c>
       <c r="Z36" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="144"/>
         <v>0.83</v>
       </c>
       <c r="AA36" s="8"/>
@@ -4846,67 +4844,67 @@
       <c r="AC36" s="8"/>
       <c r="AD36" s="8"/>
       <c r="AG36" s="8">
-        <f t="shared" ref="AG36:AL36" si="141">AG21/AG19</f>
+        <f t="shared" ref="AG36:AL36" si="145">AG21/AG19</f>
         <v>0.67735360899372454</v>
       </c>
       <c r="AH36" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="145"/>
         <v>0.77987779924495215</v>
       </c>
       <c r="AI36" s="8">
-        <f t="shared" si="141"/>
-        <v>0.8</v>
-      </c>
-      <c r="AJ36" s="8">
-        <f t="shared" si="141"/>
-        <v>0.8</v>
-      </c>
-      <c r="AK36" s="8">
-        <f t="shared" si="141"/>
-        <v>0.8265839169124346</v>
-      </c>
-      <c r="AL36" s="8">
-        <f t="shared" si="141"/>
-        <v>0.8</v>
-      </c>
-      <c r="AM36" s="8">
-        <f t="shared" ref="AM36" si="142">AM21/AM19</f>
-        <v>0.8</v>
-      </c>
-      <c r="AN36" s="8">
-        <f t="shared" ref="AN36:AO36" si="143">AN21/AN19</f>
-        <v>0.8</v>
-      </c>
-      <c r="AO36" s="8">
-        <f t="shared" si="143"/>
-        <v>0.8</v>
-      </c>
-      <c r="AP36" s="8">
-        <f t="shared" ref="AP36:AQ36" si="144">AP21/AP19</f>
-        <v>0.8</v>
-      </c>
-      <c r="AQ36" s="8">
-        <f t="shared" si="144"/>
-        <v>0.8</v>
-      </c>
-      <c r="AR36" s="8">
-        <f t="shared" ref="AR36:AV36" si="145">AR21/AR19</f>
-        <v>0.8</v>
-      </c>
-      <c r="AS36" s="8">
         <f t="shared" si="145"/>
         <v>0.8</v>
       </c>
-      <c r="AT36" s="8">
+      <c r="AJ36" s="8">
         <f t="shared" si="145"/>
         <v>0.8</v>
       </c>
-      <c r="AU36" s="8">
+      <c r="AK36" s="8">
+        <f t="shared" si="145"/>
+        <v>0.8265839169124346</v>
+      </c>
+      <c r="AL36" s="8">
         <f t="shared" si="145"/>
         <v>0.8</v>
       </c>
+      <c r="AM36" s="8">
+        <f t="shared" ref="AM36" si="146">AM21/AM19</f>
+        <v>0.8</v>
+      </c>
+      <c r="AN36" s="8">
+        <f t="shared" ref="AN36:AO36" si="147">AN21/AN19</f>
+        <v>0.8</v>
+      </c>
+      <c r="AO36" s="8">
+        <f t="shared" si="147"/>
+        <v>0.8</v>
+      </c>
+      <c r="AP36" s="8">
+        <f t="shared" ref="AP36:AQ36" si="148">AP21/AP19</f>
+        <v>0.8</v>
+      </c>
+      <c r="AQ36" s="8">
+        <f t="shared" si="148"/>
+        <v>0.80000000000000016</v>
+      </c>
+      <c r="AR36" s="8">
+        <f t="shared" ref="AR36:AV36" si="149">AR21/AR19</f>
+        <v>0.8</v>
+      </c>
+      <c r="AS36" s="8">
+        <f t="shared" si="149"/>
+        <v>0.8</v>
+      </c>
+      <c r="AT36" s="8">
+        <f t="shared" si="149"/>
+        <v>0.8</v>
+      </c>
+      <c r="AU36" s="8">
+        <f t="shared" si="149"/>
+        <v>0.8</v>
+      </c>
       <c r="AV36" s="8">
-        <f t="shared" si="145"/>
+        <f t="shared" si="149"/>
         <v>0.8</v>
       </c>
       <c r="AX36" t="s">
@@ -4935,19 +4933,19 @@
       <c r="P37" s="8"/>
       <c r="Q37" s="8"/>
       <c r="R37" s="8">
-        <f t="shared" ref="R37:U37" si="146">+R22/N22-1</f>
+        <f t="shared" ref="R37:U37" si="150">+R22/N22-1</f>
         <v>-0.19218011596305584</v>
       </c>
       <c r="S37" s="8">
-        <f t="shared" si="146"/>
+        <f t="shared" si="150"/>
         <v>2.3468737716694443E-2</v>
       </c>
       <c r="T37" s="8">
-        <f t="shared" si="146"/>
+        <f t="shared" si="150"/>
         <v>1.6866166319710718E-2</v>
       </c>
       <c r="U37" s="8">
-        <f t="shared" si="146"/>
+        <f t="shared" si="150"/>
         <v>0.15824719330624504</v>
       </c>
       <c r="V37" s="8">
@@ -4959,15 +4957,15 @@
         <v>0.21702279815389924</v>
       </c>
       <c r="X37" s="8">
-        <f t="shared" ref="X37:Z39" si="147">+X22/T22-1</f>
+        <f t="shared" ref="X37:Z39" si="151">+X22/T22-1</f>
         <v>0.64172531061651905</v>
       </c>
       <c r="Y37" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="151"/>
         <v>0.72970726054315538</v>
       </c>
       <c r="Z37" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="151"/>
         <v>0.24</v>
       </c>
       <c r="AA37" s="8"/>
@@ -4976,15 +4974,15 @@
       <c r="AD37" s="8"/>
       <c r="AG37" s="8"/>
       <c r="AH37" s="8">
-        <f t="shared" ref="AH37:AJ37" si="148">+AH22/AG22-1</f>
+        <f t="shared" ref="AH37:AJ37" si="152">+AH22/AG22-1</f>
         <v>-0.10119774579823648</v>
       </c>
       <c r="AI37" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="152"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AJ37" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="152"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AK37" s="8">
@@ -4992,47 +4990,47 @@
         <v>-0.12766364688599541</v>
       </c>
       <c r="AL37" s="8">
-        <f t="shared" ref="AL37:AQ37" si="149">+AL22/AK22-1</f>
+        <f t="shared" ref="AL37:AQ37" si="153">+AL22/AK22-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="AM37" s="8">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AN37" s="8">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AO37" s="8">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AP37" s="8">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AQ37" s="8">
-        <f t="shared" si="149"/>
+        <f t="shared" si="153"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AR37" s="8">
-        <f t="shared" ref="AR37:AR39" si="150">+AR22/AQ22-1</f>
+        <f t="shared" ref="AR37:AR39" si="154">+AR22/AQ22-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="AS37" s="8">
-        <f t="shared" ref="AS37:AS39" si="151">+AS22/AR22-1</f>
+        <f t="shared" ref="AS37:AS39" si="155">+AS22/AR22-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="AT37" s="8">
-        <f t="shared" ref="AT37:AT39" si="152">+AT22/AS22-1</f>
+        <f t="shared" ref="AT37:AT39" si="156">+AT22/AS22-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="AU37" s="8">
-        <f t="shared" ref="AU37:AU39" si="153">+AU22/AT22-1</f>
+        <f t="shared" ref="AU37:AU39" si="157">+AU22/AT22-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="AV37" s="8">
-        <f t="shared" ref="AV37:AV39" si="154">+AV22/AU22-1</f>
+        <f t="shared" ref="AV37:AV39" si="158">+AV22/AU22-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="AX37" t="s">
@@ -5040,7 +5038,7 @@
       </c>
       <c r="AY37" s="3">
         <f>NPV(AY36,AM30:DR30)</f>
-        <v>664633.29800124827</v>
+        <v>670552.72877872235</v>
       </c>
     </row>
     <row r="38" spans="2:51" x14ac:dyDescent="0.25">
@@ -5062,39 +5060,39 @@
       <c r="P38" s="8"/>
       <c r="Q38" s="8"/>
       <c r="R38" s="8">
-        <f t="shared" ref="R38:R39" si="155">+R23/N23-1</f>
+        <f t="shared" ref="R38:R39" si="159">+R23/N23-1</f>
         <v>-7.0169665057773778E-2</v>
       </c>
       <c r="S38" s="8">
-        <f t="shared" ref="S38:S39" si="156">+S23/O23-1</f>
+        <f t="shared" ref="S38:S39" si="160">+S23/O23-1</f>
         <v>0.18510601915184721</v>
       </c>
       <c r="T38" s="8">
-        <f t="shared" ref="T38:T39" si="157">+T23/P23-1</f>
+        <f t="shared" ref="T38:T39" si="161">+T23/P23-1</f>
         <v>3.2708505259297027E-2</v>
       </c>
       <c r="U38" s="8">
-        <f t="shared" ref="U38:W39" si="158">+U23/Q23-1</f>
+        <f t="shared" ref="U38:W39" si="162">+U23/Q23-1</f>
         <v>3.6821242657242514E-2</v>
       </c>
       <c r="V38" s="8">
-        <f t="shared" si="158"/>
+        <f t="shared" si="162"/>
         <v>0.23178261040544257</v>
       </c>
       <c r="W38" s="8">
-        <f t="shared" si="158"/>
+        <f t="shared" si="162"/>
         <v>0.23914820960488647</v>
       </c>
       <c r="X38" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="151"/>
         <v>0.71291762855475782</v>
       </c>
       <c r="Y38" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="151"/>
         <v>0.66042146476278218</v>
       </c>
       <c r="Z38" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="151"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AA38" s="8"/>
@@ -5103,15 +5101,15 @@
       <c r="AD38" s="8"/>
       <c r="AG38" s="8"/>
       <c r="AH38" s="8">
-        <f t="shared" ref="AH38:AJ38" si="159">+AH23/AG23-1</f>
+        <f t="shared" ref="AH38:AJ38" si="163">+AH23/AG23-1</f>
         <v>-0.30887347055256298</v>
       </c>
       <c r="AI38" s="8">
-        <f t="shared" si="159"/>
+        <f t="shared" si="163"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AJ38" s="8">
-        <f t="shared" si="159"/>
+        <f t="shared" si="163"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AK38" s="8">
@@ -5119,55 +5117,55 @@
         <v>-0.26883604114300652</v>
       </c>
       <c r="AL38" s="8">
-        <f t="shared" ref="AL38:AQ38" si="160">+AL23/AK23-1</f>
+        <f t="shared" ref="AL38:AQ38" si="164">+AL23/AK23-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="AM38" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="164"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AN38" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="164"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AO38" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="164"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AP38" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="164"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AQ38" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="164"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AR38" s="8">
-        <f t="shared" si="150"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AS38" s="8">
-        <f t="shared" si="151"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AT38" s="8">
-        <f t="shared" si="152"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AU38" s="8">
-        <f t="shared" si="153"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AV38" s="8">
         <f t="shared" si="154"/>
         <v>0.10000000000000009</v>
       </c>
+      <c r="AS38" s="8">
+        <f t="shared" si="155"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AT38" s="8">
+        <f t="shared" si="156"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AU38" s="8">
+        <f t="shared" si="157"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AV38" s="8">
+        <f t="shared" si="158"/>
+        <v>0.10000000000000009</v>
+      </c>
       <c r="AX38" t="s">
         <v>118</v>
       </c>
       <c r="AY38" s="1">
         <f>AY37/Main!L3</f>
-        <v>258.51159004327042</v>
+        <v>260.81397463194179</v>
       </c>
     </row>
     <row r="39" spans="2:51" x14ac:dyDescent="0.25">
@@ -5189,19 +5187,19 @@
       <c r="P39" s="8"/>
       <c r="Q39" s="8"/>
       <c r="R39" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="159"/>
         <v>-0.45050780050980233</v>
       </c>
       <c r="S39" s="8">
-        <f t="shared" si="156"/>
+        <f t="shared" si="160"/>
         <v>-2.6354611502412362E-2</v>
       </c>
       <c r="T39" s="8">
-        <f t="shared" si="157"/>
+        <f t="shared" si="161"/>
         <v>0.56695604620958373</v>
       </c>
       <c r="U39" s="8">
-        <f t="shared" si="158"/>
+        <f t="shared" si="162"/>
         <v>9.6199109222802726E-2</v>
       </c>
       <c r="V39" s="8">
@@ -5209,19 +5207,19 @@
         <v>0.32314081702044972</v>
       </c>
       <c r="W39" s="8">
-        <f t="shared" ref="W39" si="161">+W24/S24-1</f>
+        <f t="shared" ref="W39" si="165">+W24/S24-1</f>
         <v>0.22652342815479787</v>
       </c>
       <c r="X39" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="151"/>
         <v>0.18232779304628544</v>
       </c>
       <c r="Y39" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="151"/>
         <v>0.78048646208392536</v>
       </c>
       <c r="Z39" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="151"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="AA39" s="8"/>
@@ -5230,15 +5228,15 @@
       <c r="AD39" s="8"/>
       <c r="AG39" s="8"/>
       <c r="AH39" s="8">
-        <f t="shared" ref="AH39:AJ39" si="162">+AH24/AG24-1</f>
+        <f t="shared" ref="AH39:AJ39" si="166">+AH24/AG24-1</f>
         <v>-8.6507609299657506E-2</v>
       </c>
       <c r="AI39" s="8">
-        <f t="shared" si="162"/>
+        <f t="shared" si="166"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AJ39" s="8">
-        <f t="shared" si="162"/>
+        <f t="shared" si="166"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AK39" s="8">
@@ -5246,47 +5244,47 @@
         <v>-0.42551271990361805</v>
       </c>
       <c r="AL39" s="8">
-        <f t="shared" ref="AL39:AQ39" si="163">+AL24/AK24-1</f>
+        <f t="shared" ref="AL39:AQ39" si="167">+AL24/AK24-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="AM39" s="8">
-        <f t="shared" si="163"/>
+        <f t="shared" si="167"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AN39" s="8">
-        <f t="shared" si="163"/>
+        <f t="shared" si="167"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AO39" s="8">
-        <f t="shared" si="163"/>
+        <f t="shared" si="167"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AP39" s="8">
-        <f t="shared" si="163"/>
+        <f t="shared" si="167"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AQ39" s="8">
-        <f t="shared" si="163"/>
+        <f t="shared" si="167"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AR39" s="8">
-        <f t="shared" si="150"/>
+        <f t="shared" si="154"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AS39" s="8">
-        <f t="shared" si="151"/>
+        <f t="shared" si="155"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AT39" s="8">
-        <f t="shared" si="152"/>
+        <f t="shared" si="156"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AU39" s="8">
-        <f t="shared" si="153"/>
+        <f t="shared" si="157"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AV39" s="8">
-        <f t="shared" si="154"/>
+        <f t="shared" si="158"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AX39" t="s">
@@ -5364,52 +5362,52 @@
         <v>3674.1790000000001</v>
       </c>
       <c r="AK41" s="3">
-        <f t="shared" ref="AK41:AK46" si="164">+V41</f>
+        <f t="shared" ref="AK41:AK46" si="168">+V41</f>
         <v>5229.9870000000001</v>
       </c>
       <c r="AL41" s="3">
-        <f>+AK41+AL30</f>
-        <v>7496.3871888000003</v>
+        <f t="shared" ref="AL41:AV41" si="169">+AK41+AL30</f>
+        <v>7522.5364800000007</v>
       </c>
       <c r="AM41" s="3">
-        <f>+AL41+AM30</f>
-        <v>11745.372004872001</v>
+        <f t="shared" si="169"/>
+        <v>11815.713598200002</v>
       </c>
       <c r="AN41" s="3">
-        <f>+AM41+AN30</f>
-        <v>18780.965698530483</v>
+        <f t="shared" si="169"/>
+        <v>18920.396334138004</v>
       </c>
       <c r="AO41" s="3">
-        <f>+AN41+AO30</f>
-        <v>29350.229249076227</v>
+        <f t="shared" si="169"/>
+        <v>29590.070260320426</v>
       </c>
       <c r="AP41" s="3">
-        <f>+AO41+AP30</f>
-        <v>44445.008819930888</v>
+        <f t="shared" si="169"/>
+        <v>44825.048707070266</v>
       </c>
       <c r="AQ41" s="3">
-        <f>+AP41+AQ30</f>
-        <v>65044.939853957607</v>
+        <f t="shared" si="169"/>
+        <v>65613.380471287703</v>
       </c>
       <c r="AR41" s="3">
-        <f>+AQ41+AR30</f>
-        <v>91987.615727822602</v>
+        <f t="shared" si="169"/>
+        <v>92799.962426147613</v>
       </c>
       <c r="AS41" s="3">
-        <f>+AR41+AS30</f>
-        <v>125821.29807799682</v>
+        <f t="shared" si="169"/>
+        <v>126938.05168969333</v>
       </c>
       <c r="AT41" s="3">
-        <f>+AS41+AT30</f>
-        <v>168084.25455590629</v>
+        <f t="shared" si="169"/>
+        <v>169579.07084528217</v>
       </c>
       <c r="AU41" s="3">
-        <f>+AT41+AU30</f>
-        <v>220639.29670921969</v>
+        <f t="shared" si="169"/>
+        <v>222601.71228779142</v>
       </c>
       <c r="AV41" s="3">
-        <f>+AU41+AV30</f>
-        <v>285740.4573334232</v>
+        <f t="shared" si="169"/>
+        <v>288279.16930184886</v>
       </c>
     </row>
     <row r="42" spans="2:51" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5467,7 +5465,7 @@
         <v>364.78399999999999</v>
       </c>
       <c r="AK42" s="3">
-        <f t="shared" si="164"/>
+        <f t="shared" si="168"/>
         <v>575.048</v>
       </c>
     </row>
@@ -5526,7 +5524,7 @@
         <v>99.655000000000001</v>
       </c>
       <c r="AK43" s="3">
-        <f t="shared" si="164"/>
+        <f t="shared" si="168"/>
         <v>129.25399999999999</v>
       </c>
     </row>
@@ -5585,7 +5583,7 @@
         <v>47.758000000000003</v>
       </c>
       <c r="AK44" s="3">
-        <f t="shared" si="164"/>
+        <f t="shared" si="168"/>
         <v>39.637999999999998</v>
       </c>
     </row>
@@ -5644,7 +5642,7 @@
         <v>182.863</v>
       </c>
       <c r="AK45" s="3">
-        <f t="shared" si="164"/>
+        <f t="shared" si="168"/>
         <v>200.74</v>
       </c>
     </row>
@@ -5703,7 +5701,7 @@
         <v>153.18600000000001</v>
       </c>
       <c r="AK46" s="3">
-        <f t="shared" si="164"/>
+        <f t="shared" si="168"/>
         <v>166.21700000000001</v>
       </c>
     </row>
@@ -5727,47 +5725,47 @@
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4">
-        <f t="shared" ref="O47:X47" si="165">SUM(O41:O46)</f>
+        <f t="shared" ref="O47:X47" si="170">SUM(O41:O46)</f>
         <v>3683.1379999999995</v>
       </c>
       <c r="P47" s="4">
-        <f t="shared" si="165"/>
+        <f t="shared" si="170"/>
         <v>3980.2640000000001</v>
       </c>
       <c r="Q47" s="4">
-        <f t="shared" si="165"/>
+        <f t="shared" si="170"/>
         <v>4193.4169999999995</v>
       </c>
       <c r="R47" s="4">
-        <f t="shared" si="165"/>
+        <f t="shared" si="170"/>
         <v>4522.4250000000002</v>
       </c>
       <c r="S47" s="4">
-        <f t="shared" si="165"/>
+        <f t="shared" si="170"/>
         <v>4807.0790000000006</v>
       </c>
       <c r="T47" s="4">
-        <f t="shared" si="165"/>
+        <f t="shared" si="170"/>
         <v>5191.8800000000019</v>
       </c>
       <c r="U47" s="4">
-        <f t="shared" si="165"/>
+        <f t="shared" si="170"/>
         <v>5768.0969999999998</v>
       </c>
       <c r="V47" s="4">
-        <f t="shared" si="165"/>
+        <f t="shared" si="170"/>
         <v>6340.8839999999991</v>
       </c>
       <c r="W47" s="4">
-        <f t="shared" si="165"/>
+        <f t="shared" si="170"/>
         <v>6736.9170000000004</v>
       </c>
       <c r="X47" s="4">
-        <f t="shared" si="165"/>
+        <f t="shared" si="170"/>
         <v>7365.688000000001</v>
       </c>
       <c r="Y47" s="4">
-        <f t="shared" ref="Y47" si="166">SUM(Y41:Y46)</f>
+        <f t="shared" ref="Y47" si="171">SUM(Y41:Y46)</f>
         <v>8113.9600000000009</v>
       </c>
       <c r="AJ47" s="4">
@@ -5837,7 +5835,7 @@
         <v>12.122</v>
       </c>
       <c r="AK49" s="3">
-        <f t="shared" ref="AK49:AK55" si="167">+V49</f>
+        <f t="shared" ref="AK49:AK55" si="172">+V49</f>
         <v>0.10299999999999999</v>
       </c>
     </row>
@@ -5896,7 +5894,7 @@
         <v>222.99100000000001</v>
       </c>
       <c r="AK50" s="3">
-        <f t="shared" si="167"/>
+        <f t="shared" si="172"/>
         <v>427.04599999999999</v>
       </c>
     </row>
@@ -5968,7 +5966,7 @@
         <v>274.94800000000004</v>
       </c>
       <c r="AK51" s="3">
-        <f t="shared" si="167"/>
+        <f t="shared" si="172"/>
         <v>299.50900000000001</v>
       </c>
     </row>
@@ -6040,7 +6038,7 @@
         <v>211.30500000000001</v>
       </c>
       <c r="AK52" s="3">
-        <f t="shared" si="167"/>
+        <f t="shared" si="172"/>
         <v>266.91500000000002</v>
       </c>
     </row>
@@ -6112,7 +6110,7 @@
         <v>229.392</v>
       </c>
       <c r="AK53" s="3">
-        <f t="shared" si="167"/>
+        <f t="shared" si="172"/>
         <v>239.21899999999999</v>
       </c>
     </row>
@@ -6171,7 +6169,7 @@
         <v>10.702</v>
       </c>
       <c r="AK54" s="3">
-        <f t="shared" si="167"/>
+        <f t="shared" si="172"/>
         <v>13.685</v>
       </c>
     </row>
@@ -6230,7 +6228,7 @@
         <v>3560.9650000000001</v>
       </c>
       <c r="AK55" s="3">
-        <f t="shared" si="167"/>
+        <f t="shared" si="172"/>
         <v>5094.4070000000002</v>
       </c>
     </row>
@@ -6254,47 +6252,47 @@
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4">
-        <f t="shared" ref="O56:X56" si="168">SUM(O49:O55)</f>
+        <f t="shared" ref="O56:X56" si="173">SUM(O49:O55)</f>
         <v>3683.1379999999999</v>
       </c>
       <c r="P56" s="4">
-        <f t="shared" si="168"/>
+        <f t="shared" si="173"/>
         <v>3980.2639999999997</v>
       </c>
       <c r="Q56" s="4">
-        <f t="shared" si="168"/>
+        <f t="shared" si="173"/>
         <v>4193.4169999999995</v>
       </c>
       <c r="R56" s="4">
-        <f t="shared" si="168"/>
+        <f t="shared" si="173"/>
         <v>4522.4250000000002</v>
       </c>
       <c r="S56" s="4">
-        <f t="shared" si="168"/>
+        <f t="shared" si="173"/>
         <v>4807.0789999999997</v>
       </c>
       <c r="T56" s="4">
-        <f t="shared" si="168"/>
+        <f t="shared" si="173"/>
         <v>5191.8799999999992</v>
       </c>
       <c r="U56" s="4">
-        <f t="shared" si="168"/>
+        <f t="shared" si="173"/>
         <v>5768.0969999999998</v>
       </c>
       <c r="V56" s="4">
-        <f t="shared" si="168"/>
+        <f t="shared" si="173"/>
         <v>6340.884</v>
       </c>
       <c r="W56" s="4">
-        <f t="shared" si="168"/>
+        <f t="shared" si="173"/>
         <v>6736.9169999999995</v>
       </c>
       <c r="X56" s="4">
-        <f t="shared" si="168"/>
+        <f t="shared" si="173"/>
         <v>7365.6880000000001</v>
       </c>
       <c r="Y56" s="4">
-        <f t="shared" ref="Y56" si="169">SUM(Y49:Y55)</f>
+        <f t="shared" ref="Y56" si="174">SUM(Y49:Y55)</f>
         <v>8113.96</v>
       </c>
       <c r="AJ56" s="4">
@@ -6320,27 +6318,27 @@
       </c>
       <c r="R58" s="4"/>
       <c r="S58" s="4">
-        <f t="shared" ref="S58:X58" si="170">+S30</f>
+        <f t="shared" ref="S58:X58" si="175">+S30</f>
         <v>231.18099999999993</v>
       </c>
       <c r="T58" s="4">
-        <f t="shared" si="170"/>
+        <f t="shared" si="175"/>
         <v>225.89000000000001</v>
       </c>
       <c r="U58" s="4">
-        <f t="shared" si="170"/>
+        <f t="shared" si="175"/>
         <v>285.95000000000005</v>
       </c>
       <c r="V58" s="4">
-        <f t="shared" si="170"/>
+        <f t="shared" si="175"/>
         <v>343.96600000000001</v>
       </c>
       <c r="W58" s="4">
-        <f t="shared" si="170"/>
+        <f t="shared" si="175"/>
         <v>375.37400000000008</v>
       </c>
       <c r="X58" s="4">
-        <f t="shared" si="170"/>
+        <f t="shared" si="175"/>
         <v>322.279</v>
       </c>
       <c r="Y58" s="4">
@@ -6360,7 +6358,7 @@
         <v>-172.64291000000003</v>
       </c>
       <c r="AK58" s="3">
-        <f t="shared" ref="AK58:AK66" si="171">SUM(S58:V58)</f>
+        <f t="shared" ref="AK58:AK66" si="176">SUM(S58:V58)</f>
         <v>1086.9870000000001</v>
       </c>
     </row>
@@ -6408,7 +6406,7 @@
         <v>217.375</v>
       </c>
       <c r="AK59" s="3">
-        <f t="shared" si="171"/>
+        <f t="shared" si="176"/>
         <v>467.91800000000001</v>
       </c>
     </row>
@@ -6456,7 +6454,7 @@
         <v>33.353999999999999</v>
       </c>
       <c r="AK60" s="3">
-        <f t="shared" si="171"/>
+        <f t="shared" si="176"/>
         <v>31.586999999999996</v>
       </c>
     </row>
@@ -6504,7 +6502,7 @@
         <v>475.90300000000002</v>
       </c>
       <c r="AK61" s="3">
-        <f t="shared" si="171"/>
+        <f t="shared" si="176"/>
         <v>691.63800000000003</v>
       </c>
     </row>
@@ -6551,7 +6549,7 @@
         <v>47.018999999999998</v>
       </c>
       <c r="AK62" s="3">
-        <f t="shared" si="171"/>
+        <f t="shared" si="176"/>
         <v>41.238999999999997</v>
       </c>
     </row>
@@ -6599,7 +6597,7 @@
         <v>13.16</v>
       </c>
       <c r="AK63" s="3">
-        <f t="shared" si="171"/>
+        <f t="shared" si="176"/>
         <v>19.306000000000001</v>
       </c>
     </row>
@@ -6647,7 +6645,7 @@
         <v>-46.609000000000002</v>
       </c>
       <c r="AK64" s="3">
-        <f t="shared" si="171"/>
+        <f t="shared" si="176"/>
         <v>-52.521000000000001</v>
       </c>
     </row>
@@ -6698,7 +6696,7 @@
         <v>-34.255000000000003</v>
       </c>
       <c r="AK65" s="3">
-        <f t="shared" si="171"/>
+        <f t="shared" si="176"/>
         <v>24.795000000000002</v>
       </c>
     </row>
@@ -6770,7 +6768,7 @@
         <v>6.2360000000000042</v>
       </c>
       <c r="AK66" s="3">
-        <f t="shared" si="171"/>
+        <f t="shared" si="176"/>
         <v>-70.097000000000051</v>
       </c>
     </row>
@@ -6784,31 +6782,31 @@
       </c>
       <c r="R67" s="4"/>
       <c r="S67" s="4">
-        <f t="shared" ref="S67:Y67" si="172">SUM(S59:S66)</f>
+        <f t="shared" ref="S67:Y67" si="177">SUM(S59:S66)</f>
         <v>129.57900000000001</v>
       </c>
       <c r="T67" s="4">
-        <f t="shared" si="172"/>
+        <f t="shared" si="177"/>
         <v>144.18699999999995</v>
       </c>
       <c r="U67" s="4">
-        <f t="shared" si="172"/>
+        <f t="shared" si="177"/>
         <v>419.77199999999976</v>
       </c>
       <c r="V67" s="4">
-        <f t="shared" si="172"/>
+        <f t="shared" si="177"/>
         <v>460.32700000000017</v>
       </c>
       <c r="W67" s="4">
-        <f t="shared" si="172"/>
+        <f t="shared" si="177"/>
         <v>310.26299999999998</v>
       </c>
       <c r="X67" s="4">
-        <f t="shared" si="172"/>
+        <f t="shared" si="177"/>
         <v>539.25099999999998</v>
       </c>
       <c r="Y67" s="4">
-        <f t="shared" si="172"/>
+        <f t="shared" si="177"/>
         <v>507.66400000000004</v>
       </c>
       <c r="Z67" s="3"/>
@@ -6973,27 +6971,27 @@
       </c>
       <c r="R72" s="4"/>
       <c r="S72" s="4">
-        <f t="shared" ref="S72:X72" si="173">SUM(S70:S71)</f>
+        <f t="shared" ref="S72:X72" si="178">SUM(S70:S71)</f>
         <v>-511.245</v>
       </c>
       <c r="T72" s="4">
-        <f t="shared" si="173"/>
+        <f t="shared" si="178"/>
         <v>-148.8779999999999</v>
       </c>
       <c r="U72" s="4">
-        <f t="shared" si="173"/>
+        <f t="shared" si="178"/>
         <v>-320.726</v>
       </c>
       <c r="V72" s="4">
-        <f t="shared" si="173"/>
+        <f t="shared" si="178"/>
         <v>640.65899999999999</v>
       </c>
       <c r="W72" s="4">
-        <f t="shared" si="173"/>
+        <f t="shared" si="178"/>
         <v>-1390.277</v>
       </c>
       <c r="X72" s="4">
-        <f t="shared" si="173"/>
+        <f t="shared" si="178"/>
         <v>-617.01000000000022</v>
       </c>
     </row>
@@ -7105,27 +7103,27 @@
       </c>
       <c r="R77" s="4"/>
       <c r="S77" s="4">
-        <f t="shared" ref="S77:X77" si="174">SUM(S74:S76)</f>
+        <f t="shared" ref="S77:X77" si="179">SUM(S74:S76)</f>
         <v>75.248000000000005</v>
       </c>
       <c r="T77" s="4">
-        <f t="shared" si="174"/>
+        <f t="shared" si="179"/>
         <v>-1.9750000000000005</v>
       </c>
       <c r="U77" s="4">
-        <f t="shared" si="174"/>
+        <f t="shared" si="179"/>
         <v>151.42699999999999</v>
       </c>
       <c r="V77" s="4">
-        <f t="shared" si="174"/>
+        <f t="shared" si="179"/>
         <v>238.66400000000002</v>
       </c>
       <c r="W77" s="4">
-        <f t="shared" si="174"/>
+        <f t="shared" si="179"/>
         <v>-28.896999999999991</v>
       </c>
       <c r="X77" s="4">
-        <f t="shared" si="174"/>
+        <f t="shared" si="179"/>
         <v>6.4499999999999789</v>
       </c>
     </row>
@@ -7174,23 +7172,23 @@
         <v>-310.44200000000001</v>
       </c>
       <c r="T79" s="4">
-        <f t="shared" ref="T79:X79" si="175">+T78+T77+T72+T67</f>
+        <f t="shared" ref="T79:X79" si="180">+T78+T77+T72+T67</f>
         <v>-7.5899999999999466</v>
       </c>
       <c r="U79" s="4">
-        <f t="shared" si="175"/>
+        <f t="shared" si="180"/>
         <v>256.38099999999974</v>
       </c>
       <c r="V79" s="4">
-        <f t="shared" si="175"/>
+        <f t="shared" si="180"/>
         <v>1331.9450000000002</v>
       </c>
       <c r="W79" s="4">
-        <f t="shared" si="175"/>
+        <f t="shared" si="180"/>
         <v>-1104.931</v>
       </c>
       <c r="X79" s="4">
-        <f t="shared" si="175"/>
+        <f t="shared" si="180"/>
         <v>-63.771000000000299</v>
       </c>
     </row>
